--- a/data/coding/P02.xlsx
+++ b/data/coding/P02.xlsx
@@ -11,7 +11,7 @@
     <sheet name="코드표" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'coding'!$A$1:$G$1205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'coding'!$A$1:$G$1207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1205"/>
+  <dimension ref="A1:G1207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -27290,11 +27290,11 @@
       </c>
       <c r="E990" s="8" t="inlineStr">
         <is>
-          <t>여기서 너무 오래 고민하면 안 돼.</t>
+          <t>① 분야를 확정하기 (가장 중요)</t>
         </is>
       </c>
       <c r="F990" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G990" s="6" t="inlineStr"/>
     </row>
@@ -27317,11 +27317,11 @@
       </c>
       <c r="E991" s="8" t="inlineStr">
         <is>
-          <t>나는 너라면</t>
+          <t>여기서 너무 오래 고민하면 안 돼.</t>
         </is>
       </c>
       <c r="F991" s="7" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G991" s="6" t="inlineStr"/>
     </row>
@@ -27344,11 +27344,11 @@
       </c>
       <c r="E992" s="8" t="inlineStr">
         <is>
-          <t>1순위 Robot Learning / Physical AI 2순위 Manufacturing AI 3순위 Multimodal AI</t>
+          <t>나는 너라면</t>
         </is>
       </c>
       <c r="F992" s="7" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="G992" s="6" t="inlineStr"/>
     </row>
@@ -27371,11 +27371,11 @@
       </c>
       <c r="E993" s="8" t="inlineStr">
         <is>
-          <t>이렇게 정한다.</t>
+          <t>1순위 Robot Learning / Physical AI 2순위 Manufacturing AI 3순위 Multimodal AI</t>
         </is>
       </c>
       <c r="F993" s="7" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="G993" s="6" t="inlineStr"/>
     </row>
@@ -27398,11 +27398,11 @@
       </c>
       <c r="E994" s="8" t="inlineStr">
         <is>
-          <t>LLM 연구실 ❌ 제외가 아니라 LLM을 활용하는 연구실 로 생각하면 된다.</t>
+          <t>이렇게 정한다.</t>
         </is>
       </c>
       <c r="F994" s="7" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="G994" s="6" t="inlineStr"/>
     </row>
@@ -27425,11 +27425,11 @@
       </c>
       <c r="E995" s="8" t="inlineStr">
         <is>
-          <t>오전 10:30 ~ 12:30</t>
+          <t>LLM 연구실 ❌ 제외가 아니라 LLM을 활용하는 연구실 로 생각하면 된다.</t>
         </is>
       </c>
       <c r="F995" s="7" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G995" s="6" t="inlineStr"/>
     </row>
@@ -27452,11 +27452,11 @@
       </c>
       <c r="E996" s="8" t="inlineStr">
         <is>
-          <t>② 교수님 후보 찾기</t>
+          <t>오전 10:30 ~ 12:30</t>
         </is>
       </c>
       <c r="F996" s="7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G996" s="6" t="inlineStr"/>
     </row>
@@ -27479,11 +27479,11 @@
       </c>
       <c r="E997" s="8" t="inlineStr">
         <is>
-          <t>여기가 오늘의 핵심이다.</t>
+          <t>② 교수님 후보 찾기</t>
         </is>
       </c>
       <c r="F997" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G997" s="6" t="inlineStr"/>
     </row>
@@ -27506,11 +27506,11 @@
       </c>
       <c r="E998" s="8" t="inlineStr">
         <is>
-          <t>예를 들어 KAIST UNIST POSTECH SNU 고려대 연세대 이렇게 보고 교수님을 10명 정도 뽑는다.</t>
+          <t>여기가 오늘의 핵심이다.</t>
         </is>
       </c>
       <c r="F998" s="7" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="G998" s="6" t="inlineStr"/>
     </row>
@@ -27533,11 +27533,11 @@
       </c>
       <c r="E999" s="8" t="inlineStr">
         <is>
-          <t>각 교수마다</t>
+          <t>예를 들어 KAIST UNIST POSTECH SNU 고려대 연세대 이렇게 보고 교수님을 10명 정도 뽑는다.</t>
         </is>
       </c>
       <c r="F999" s="7" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="G999" s="6" t="inlineStr"/>
     </row>
@@ -27560,11 +27560,11 @@
       </c>
       <c r="E1000" s="8" t="inlineStr">
         <is>
-          <t>딱 이것만 적어.</t>
+          <t>각 교수마다</t>
         </is>
       </c>
       <c r="F1000" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G1000" s="6" t="inlineStr"/>
     </row>
@@ -27587,11 +27587,11 @@
       </c>
       <c r="E1001" s="8" t="inlineStr">
         <is>
-          <t>교수명 연구분야 최근 논문 내가 흥미있는 이유 컨택 여부</t>
+          <t>딱 이것만 적어.</t>
         </is>
       </c>
       <c r="F1001" s="7" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G1001" s="6" t="inlineStr"/>
     </row>
@@ -27614,11 +27614,11 @@
       </c>
       <c r="E1002" s="8" t="inlineStr">
         <is>
-          <t>5줄이면 된다.</t>
+          <t>교수명 연구분야 최근 논문 내가 흥미있는 이유 컨택 여부</t>
         </is>
       </c>
       <c r="F1002" s="7" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="G1002" s="6" t="inlineStr"/>
     </row>
@@ -27641,11 +27641,11 @@
       </c>
       <c r="E1003" s="8" t="inlineStr">
         <is>
-          <t>점심</t>
+          <t>5줄이면 된다.</t>
         </is>
       </c>
       <c r="F1003" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G1003" s="6" t="inlineStr"/>
     </row>
@@ -27668,11 +27668,11 @@
       </c>
       <c r="E1004" s="8" t="inlineStr">
         <is>
-          <t>쉬어.</t>
+          <t>점심</t>
         </is>
       </c>
       <c r="F1004" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1004" s="6" t="inlineStr"/>
     </row>
@@ -27695,11 +27695,11 @@
       </c>
       <c r="E1005" s="8" t="inlineStr">
         <is>
-          <t>오후 1:30 ~ 3:00</t>
+          <t>쉬어.</t>
         </is>
       </c>
       <c r="F1005" s="7" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G1005" s="6" t="inlineStr"/>
     </row>
@@ -27722,11 +27722,11 @@
       </c>
       <c r="E1006" s="8" t="inlineStr">
         <is>
-          <t>③ CV 수정</t>
+          <t>오후 1:30 ~ 3:00</t>
         </is>
       </c>
       <c r="F1006" s="7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G1006" s="6" t="inlineStr"/>
     </row>
@@ -27749,11 +27749,11 @@
       </c>
       <c r="E1007" s="8" t="inlineStr">
         <is>
-          <t>여기는 새로운 걸 만드는 게 아니라 정리하는 거다.</t>
+          <t>③ CV 수정</t>
         </is>
       </c>
       <c r="F1007" s="7" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G1007" s="6" t="inlineStr"/>
     </row>
@@ -27776,11 +27776,11 @@
       </c>
       <c r="E1008" s="8" t="inlineStr">
         <is>
-          <t>예를 들어</t>
+          <t>여기는 새로운 걸 만드는 게 아니라 정리하는 거다.</t>
         </is>
       </c>
       <c r="F1008" s="7" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G1008" s="6" t="inlineStr"/>
     </row>
@@ -27803,11 +27803,11 @@
       </c>
       <c r="E1009" s="8" t="inlineStr">
         <is>
-          <t>Research Interest Computer Vision Multimodal AI Robot Learning Physical AI</t>
+          <t>예를 들어</t>
         </is>
       </c>
       <c r="F1009" s="7" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="G1009" s="6" t="inlineStr"/>
     </row>
@@ -27830,11 +27830,11 @@
       </c>
       <c r="E1010" s="8" t="inlineStr">
         <is>
-          <t>이렇게 넣는다.</t>
+          <t>Research Interest Computer Vision Multimodal AI Robot Learning Physical AI</t>
         </is>
       </c>
       <c r="F1010" s="7" t="n">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="G1010" s="6" t="inlineStr"/>
     </row>
@@ -27857,11 +27857,11 @@
       </c>
       <c r="E1011" s="8" t="inlineStr">
         <is>
-          <t>그리고 Project 순서를 가장 자신 있는 순서로 바꾼다.</t>
+          <t>이렇게 넣는다.</t>
         </is>
       </c>
       <c r="F1011" s="7" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G1011" s="6" t="inlineStr"/>
     </row>
@@ -27884,11 +27884,11 @@
       </c>
       <c r="E1012" s="8" t="inlineStr">
         <is>
-          <t>오후 3:00 ~ 5:00</t>
+          <t>그리고 Project 순서를 가장 자신 있는 순서로 바꾼다.</t>
         </is>
       </c>
       <c r="F1012" s="7" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G1012" s="6" t="inlineStr"/>
     </row>
@@ -27911,11 +27911,11 @@
       </c>
       <c r="E1013" s="8" t="inlineStr">
         <is>
-          <t>④ 논문 읽기</t>
+          <t>오후 3:00 ~ 5:00</t>
         </is>
       </c>
       <c r="F1013" s="7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G1013" s="6" t="inlineStr"/>
     </row>
@@ -27938,11 +27938,11 @@
       </c>
       <c r="E1014" s="8" t="inlineStr">
         <is>
-          <t>많이 읽지 마.</t>
+          <t>④ 논문 읽기</t>
         </is>
       </c>
       <c r="F1014" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1014" s="6" t="inlineStr"/>
     </row>
@@ -27965,11 +27965,11 @@
       </c>
       <c r="E1015" s="8" t="inlineStr">
         <is>
-          <t>교수마다 1편만.</t>
+          <t>많이 읽지 마.</t>
         </is>
       </c>
       <c r="F1015" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1015" s="6" t="inlineStr"/>
     </row>
@@ -27992,11 +27992,11 @@
       </c>
       <c r="E1016" s="8" t="inlineStr">
         <is>
-          <t>읽는 것도 전부 읽는 게 아니다.</t>
+          <t>교수마다 1편만.</t>
         </is>
       </c>
       <c r="F1016" s="7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G1016" s="6" t="inlineStr"/>
     </row>
@@ -28019,11 +28019,11 @@
       </c>
       <c r="E1017" s="8" t="inlineStr">
         <is>
-          <t>이것만 보면 된다.</t>
+          <t>읽는 것도 전부 읽는 게 아니다.</t>
         </is>
       </c>
       <c r="F1017" s="7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G1017" s="6" t="inlineStr"/>
     </row>
@@ -28046,11 +28046,11 @@
       </c>
       <c r="E1018" s="8" t="inlineStr">
         <is>
-          <t>Abstract Introduction Figure 1 Conclusion</t>
+          <t>이것만 보면 된다.</t>
         </is>
       </c>
       <c r="F1018" s="7" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G1018" s="6" t="inlineStr"/>
     </row>
@@ -28073,11 +28073,11 @@
       </c>
       <c r="E1019" s="8" t="inlineStr">
         <is>
-          <t>여기만 봐도 70%는 이해된다.</t>
+          <t>Abstract Introduction Figure 1 Conclusion</t>
         </is>
       </c>
       <c r="F1019" s="7" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G1019" s="6" t="inlineStr"/>
     </row>
@@ -28100,11 +28100,11 @@
       </c>
       <c r="E1020" s="8" t="inlineStr">
         <is>
-          <t>오후 5:00 ~ 6:00</t>
+          <t>여기만 봐도 70%는 이해된다.</t>
         </is>
       </c>
       <c r="F1020" s="7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G1020" s="6" t="inlineStr"/>
     </row>
@@ -28127,11 +28127,11 @@
       </c>
       <c r="E1021" s="8" t="inlineStr">
         <is>
-          <t>⑤ 컨택 메일 작성</t>
+          <t>오후 5:00 ~ 6:00</t>
         </is>
       </c>
       <c r="F1021" s="7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G1021" s="6" t="inlineStr"/>
     </row>
@@ -28154,11 +28154,11 @@
       </c>
       <c r="E1022" s="8" t="inlineStr">
         <is>
-          <t>이때 메일은 교수마다 20% 정도만 수정하면 된다.</t>
+          <t>⑤ 컨택 메일 작성</t>
         </is>
       </c>
       <c r="F1022" s="7" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G1022" s="6" t="inlineStr"/>
     </row>
@@ -28181,11 +28181,11 @@
       </c>
       <c r="E1023" s="8" t="inlineStr">
         <is>
-          <t>저녁</t>
+          <t>이때 메일은 교수마다 20% 정도만 수정하면 된다.</t>
         </is>
       </c>
       <c r="F1023" s="7" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G1023" s="6" t="inlineStr"/>
     </row>
@@ -28208,11 +28208,11 @@
       </c>
       <c r="E1024" s="8" t="inlineStr">
         <is>
-          <t>⑥ 예상 질문 정리</t>
+          <t>저녁</t>
         </is>
       </c>
       <c r="F1024" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G1024" s="6" t="inlineStr"/>
     </row>
@@ -28235,11 +28235,11 @@
       </c>
       <c r="E1025" s="8" t="inlineStr">
         <is>
-          <t>예를 들어</t>
+          <t>⑥ 예상 질문 정리</t>
         </is>
       </c>
       <c r="F1025" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1025" s="6" t="inlineStr"/>
     </row>
@@ -28262,11 +28262,11 @@
       </c>
       <c r="E1026" s="8" t="inlineStr">
         <is>
-          <t>왜 우리 연구실?</t>
+          <t>예를 들어</t>
         </is>
       </c>
       <c r="F1026" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1026" s="6" t="inlineStr"/>
     </row>
@@ -28289,11 +28289,11 @@
       </c>
       <c r="E1027" s="8" t="inlineStr">
         <is>
-          <t>왜 대학원?</t>
+          <t>왜 우리 연구실?</t>
         </is>
       </c>
       <c r="F1027" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G1027" s="6" t="inlineStr"/>
     </row>
@@ -28316,11 +28316,11 @@
       </c>
       <c r="E1028" s="8" t="inlineStr">
         <is>
-          <t>왜 이 분야?</t>
+          <t>왜 대학원?</t>
         </is>
       </c>
       <c r="F1028" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1028" s="6" t="inlineStr"/>
     </row>
@@ -28343,11 +28343,11 @@
       </c>
       <c r="E1029" s="8" t="inlineStr">
         <is>
-          <t>무슨 연구를 했나요?</t>
+          <t>왜 이 분야?</t>
         </is>
       </c>
       <c r="F1029" s="7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G1029" s="6" t="inlineStr"/>
     </row>
@@ -28370,11 +28370,11 @@
       </c>
       <c r="E1030" s="8" t="inlineStr">
         <is>
-          <t>앞으로 무엇을 하고 싶나요?</t>
+          <t>무슨 연구를 했나요?</t>
         </is>
       </c>
       <c r="F1030" s="7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G1030" s="6" t="inlineStr"/>
     </row>
@@ -28397,11 +28397,11 @@
       </c>
       <c r="E1031" s="8" t="inlineStr">
         <is>
-          <t>여기만 준비하면 된다.</t>
+          <t>앞으로 무엇을 하고 싶나요?</t>
         </is>
       </c>
       <c r="F1031" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G1031" s="6" t="inlineStr"/>
     </row>
@@ -28424,7 +28424,7 @@
       </c>
       <c r="E1032" s="8" t="inlineStr">
         <is>
-          <t>내가 오늘 공부한다면?</t>
+          <t>여기만 준비하면 된다.</t>
         </is>
       </c>
       <c r="F1032" s="7" t="n">
@@ -28451,11 +28451,11 @@
       </c>
       <c r="E1033" s="8" t="inlineStr">
         <is>
-          <t>솔직히 말하면 오늘은 ROS도 안 한다.</t>
+          <t>내가 오늘 공부한다면?</t>
         </is>
       </c>
       <c r="F1033" s="7" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G1033" s="6" t="inlineStr"/>
     </row>
@@ -28478,11 +28478,11 @@
       </c>
       <c r="E1034" s="8" t="inlineStr">
         <is>
-          <t>RL도 안 한다.</t>
+          <t>솔직히 말하면 오늘은 ROS도 안 한다.</t>
         </is>
       </c>
       <c r="F1034" s="7" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G1034" s="6" t="inlineStr"/>
     </row>
@@ -28505,11 +28505,11 @@
       </c>
       <c r="E1035" s="8" t="inlineStr">
         <is>
-          <t>LLM도 안 한다.</t>
+          <t>RL도 안 한다.</t>
         </is>
       </c>
       <c r="F1035" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1035" s="6" t="inlineStr"/>
     </row>
@@ -28532,11 +28532,11 @@
       </c>
       <c r="E1036" s="8" t="inlineStr">
         <is>
-          <t>Transformer도 안 한다.</t>
+          <t>LLM도 안 한다.</t>
         </is>
       </c>
       <c r="F1036" s="7" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G1036" s="6" t="inlineStr"/>
     </row>
@@ -28559,11 +28559,11 @@
       </c>
       <c r="E1037" s="8" t="inlineStr">
         <is>
-          <t>왜냐하면 교수님은 "오늘 RL을 공부했네." 이걸 보는 게 아니다.</t>
+          <t>Transformer도 안 한다.</t>
         </is>
       </c>
       <c r="F1037" s="7" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G1037" s="6" t="inlineStr"/>
     </row>
@@ -28586,11 +28586,11 @@
       </c>
       <c r="E1038" s="8" t="inlineStr">
         <is>
-          <t>대신 교수님은 "우리 연구실에 관심을 갖고 왔는가?"를 본다.</t>
+          <t>왜냐하면 교수님은 "오늘 RL을 공부했네." 이걸 보는 게 아니다.</t>
         </is>
       </c>
       <c r="F1038" s="7" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G1038" s="6" t="inlineStr"/>
     </row>
@@ -28613,11 +28613,11 @@
       </c>
       <c r="E1039" s="8" t="inlineStr">
         <is>
-          <t>내가 오늘 하루에 가장 많이 할 것</t>
+          <t>대신 교수님은 "우리 연구실에 관심을 갖고 왔는가?"를 본다.</t>
         </is>
       </c>
       <c r="F1039" s="7" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G1039" s="6" t="inlineStr"/>
     </row>
@@ -28640,11 +28640,11 @@
       </c>
       <c r="E1040" s="8" t="inlineStr">
         <is>
-          <t>우선순위 / 할 일 / 시간</t>
+          <t>내가 오늘 하루에 가장 많이 할 것</t>
         </is>
       </c>
       <c r="F1040" s="7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G1040" s="6" t="inlineStr"/>
     </row>
@@ -28667,11 +28667,11 @@
       </c>
       <c r="E1041" s="8" t="inlineStr">
         <is>
-          <t>⭐⭐⭐⭐⭐ / 교수님 조사 / 2시간</t>
+          <t>우선순위 / 할 일 / 시간</t>
         </is>
       </c>
       <c r="F1041" s="7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G1041" s="6" t="inlineStr"/>
     </row>
@@ -28694,11 +28694,11 @@
       </c>
       <c r="E1042" s="8" t="inlineStr">
         <is>
-          <t>⭐⭐⭐⭐⭐ / CV 수정 / 1.5시간</t>
+          <t>⭐⭐⭐⭐⭐ / 교수님 조사 / 2시간</t>
         </is>
       </c>
       <c r="F1042" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1042" s="6" t="inlineStr"/>
     </row>
@@ -28721,7 +28721,7 @@
       </c>
       <c r="E1043" s="8" t="inlineStr">
         <is>
-          <t>⭐⭐⭐⭐⭐ / 연구분야 결정 / 1시간</t>
+          <t>⭐⭐⭐⭐⭐ / CV 수정 / 1.5시간</t>
         </is>
       </c>
       <c r="F1043" s="7" t="n">
@@ -28748,11 +28748,11 @@
       </c>
       <c r="E1044" s="8" t="inlineStr">
         <is>
-          <t>⭐⭐⭐⭐☆ / 논문 5편 읽기 / 2시간</t>
+          <t>⭐⭐⭐⭐⭐ / 연구분야 결정 / 1시간</t>
         </is>
       </c>
       <c r="F1044" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G1044" s="6" t="inlineStr"/>
     </row>
@@ -28775,11 +28775,11 @@
       </c>
       <c r="E1045" s="8" t="inlineStr">
         <is>
-          <t>⭐⭐⭐⭐☆ / 메일 작성 / 1시간</t>
+          <t>⭐⭐⭐⭐☆ / 논문 5편 읽기 / 2시간</t>
         </is>
       </c>
       <c r="F1045" s="7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G1045" s="6" t="inlineStr"/>
     </row>
@@ -28802,11 +28802,11 @@
       </c>
       <c r="E1046" s="8" t="inlineStr">
         <is>
-          <t>⭐⭐⭐☆☆ / 예상 질문 정리 / 1시간</t>
+          <t>⭐⭐⭐⭐☆ / 메일 작성 / 1시간</t>
         </is>
       </c>
       <c r="F1046" s="7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G1046" s="6" t="inlineStr"/>
     </row>
@@ -28829,11 +28829,11 @@
       </c>
       <c r="E1047" s="8" t="inlineStr">
         <is>
-          <t>그리고 하나 더.</t>
+          <t>⭐⭐⭐☆☆ / 예상 질문 정리 / 1시간</t>
         </is>
       </c>
       <c r="F1047" s="7" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G1047" s="6" t="inlineStr"/>
     </row>
@@ -28856,11 +28856,11 @@
       </c>
       <c r="E1048" s="8" t="inlineStr">
         <is>
-          <t>나는 오늘 하루 동안 AI 공부를 거의 안 할 거야.</t>
+          <t>그리고 하나 더.</t>
         </is>
       </c>
       <c r="F1048" s="7" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="G1048" s="6" t="inlineStr"/>
     </row>
@@ -28883,11 +28883,11 @@
       </c>
       <c r="E1049" s="8" t="inlineStr">
         <is>
-          <t>왜냐하면 지금은 실력을 키우는 단계가 아니라, "어떤 연구실이 나에게 맞는지"를 판단하는 단계이기 때문이야.</t>
+          <t>나는 오늘 하루 동안 AI 공부를 거의 안 할 거야.</t>
         </is>
       </c>
       <c r="F1049" s="7" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="G1049" s="6" t="inlineStr"/>
     </row>
@@ -28910,11 +28910,11 @@
       </c>
       <c r="E1050" s="8" t="inlineStr">
         <is>
-          <t>내가 너라면 오늘 하루의 최종 결과물은 딱 5개야.</t>
+          <t>왜냐하면 지금은 실력을 키우는 단계가 아니라, "어떤 연구실이 나에게 맞는지"를 판단하는 단계이기 때문이야.</t>
         </is>
       </c>
       <c r="F1050" s="7" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="G1050" s="6" t="inlineStr"/>
     </row>
@@ -28937,11 +28937,11 @@
       </c>
       <c r="E1051" s="8" t="inlineStr">
         <is>
-          <t>✅ 관심 분야 3개 (예: Robot Learning, Manufacturing AI, Multimodal AI)</t>
+          <t>내가 너라면 오늘 하루의 최종 결과물은 딱 5개야.</t>
         </is>
       </c>
       <c r="F1051" s="7" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G1051" s="6" t="inlineStr"/>
     </row>
@@ -28964,11 +28964,11 @@
       </c>
       <c r="E1052" s="8" t="inlineStr">
         <is>
-          <t>✅ 컨택할 교수님 10명 리스트</t>
+          <t>✅ 관심 분야 3개 (예: Robot Learning, Manufacturing AI, Multimodal AI)</t>
         </is>
       </c>
       <c r="F1052" s="7" t="n">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="G1052" s="6" t="inlineStr"/>
     </row>
@@ -28991,11 +28991,11 @@
       </c>
       <c r="E1053" s="8" t="inlineStr">
         <is>
-          <t>✅ 최신 CV (영문)</t>
+          <t>✅ 컨택할 교수님 10명 리스트</t>
         </is>
       </c>
       <c r="F1053" s="7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1053" s="6" t="inlineStr"/>
     </row>
@@ -29018,11 +29018,11 @@
       </c>
       <c r="E1054" s="8" t="inlineStr">
         <is>
-          <t>✅ 교수님별 최근 논문 핵심 메모</t>
+          <t>✅ 최신 CV (영문)</t>
         </is>
       </c>
       <c r="F1054" s="7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G1054" s="6" t="inlineStr"/>
     </row>
@@ -29045,11 +29045,11 @@
       </c>
       <c r="E1055" s="8" t="inlineStr">
         <is>
-          <t>✅ 바로 보낼 수 있는 컨택 메일 초안</t>
+          <t>✅ 교수님별 최근 논문 핵심 메모</t>
         </is>
       </c>
       <c r="F1055" s="7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G1055" s="6" t="inlineStr"/>
     </row>
@@ -29072,11 +29072,11 @@
       </c>
       <c r="E1056" s="8" t="inlineStr">
         <is>
-          <t>내가 한 가지 제안하고 싶은 건</t>
+          <t>✅ 바로 보낼 수 있는 컨택 메일 초안</t>
         </is>
       </c>
       <c r="F1056" s="7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G1056" s="6" t="inlineStr"/>
     </row>
@@ -29099,11 +29099,11 @@
       </c>
       <c r="E1057" s="8" t="inlineStr">
         <is>
-          <t>사실 지금은 "무엇을 공부할까?"보다 "누구에게 컨택할까?"가 훨씬 중요한 시기야.</t>
+          <t>내가 한 가지 제안하고 싶은 건</t>
         </is>
       </c>
       <c r="F1057" s="7" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G1057" s="6" t="inlineStr"/>
     </row>
@@ -29126,11 +29126,11 @@
       </c>
       <c r="E1058" s="8" t="inlineStr">
         <is>
-          <t>그래서 오늘이라면 나는 AI 공부 대신 국내 주요 대학의 교수님들을 전부 훑어보고, 너에게 맞는 연구실을 선별하는 데 시간을 가장 많이 투자할 거야.</t>
+          <t>사실 지금은 "무엇을 공부할까?"보다 "누구에게 컨택할까?"가 훨씬 중요한 시기야.</t>
         </is>
       </c>
       <c r="F1058" s="7" t="n">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="G1058" s="6" t="inlineStr"/>
     </row>
@@ -29153,11 +29153,11 @@
       </c>
       <c r="E1059" s="8" t="inlineStr">
         <is>
-          <t>그 작업이 끝나면 그다음부터는 "무엇을 공부해야 하는지"도 자연스럽게 정해진다.</t>
+          <t>그래서 오늘이라면 나는 AI 공부 대신 국내 주요 대학의 교수님들을 전부 훑어보고, 너에게 맞는 연구실을 선별하는 데 시간을 가장 많이 투자할 거야.</t>
         </is>
       </c>
       <c r="F1059" s="7" t="n">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="G1059" s="6" t="inlineStr"/>
     </row>
@@ -29180,73 +29180,73 @@
       </c>
       <c r="E1060" s="8" t="inlineStr">
         <is>
+          <t>그 작업이 끝나면 그다음부터는 "무엇을 공부해야 하는지"도 자연스럽게 정해진다.</t>
+        </is>
+      </c>
+      <c r="F1060" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1060" s="6" t="inlineStr"/>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="7" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B1061" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1061" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="D1061" s="7" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E1061" s="8" t="inlineStr">
+        <is>
           <t>예를 들어 로봇 중심 연구실이면 ROS와 Robot Learning을, Manufacturing AI 연구실이면 시계열·비전·이상탐지를, AI Systems 연구실이면 CUDA와 분산학습을 준비하면 되니까.</t>
         </is>
       </c>
-      <c r="F1060" s="7" t="n">
+      <c r="F1061" s="7" t="n">
         <v>115</v>
       </c>
-      <c r="G1060" s="6" t="inlineStr"/>
-    </row>
-    <row r="1061">
-      <c r="A1061" s="2" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="B1061" s="2" t="n">
+      <c r="G1061" s="6" t="inlineStr"/>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="2" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B1062" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="C1061" s="2" t="inlineStr">
+      <c r="C1062" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D1061" s="2" t="inlineStr">
+      <c r="D1062" s="2" t="inlineStr">
         <is>
           <t>Prompt</t>
         </is>
       </c>
-      <c r="E1061" s="3" t="inlineStr">
+      <c r="E1062" s="3" t="inlineStr">
         <is>
           <t>근데 답장이 안오면 어쩌지 ..</t>
         </is>
       </c>
-      <c r="F1061" s="2" t="n">
+      <c r="F1062" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="G1061" s="2" t="inlineStr">
+      <c r="G1062" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="1062">
-      <c r="A1062" s="4" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="B1062" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C1062" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1062" s="4" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E1062" s="5" t="inlineStr">
-        <is>
-          <t>그 마음은 정말 자연스러운 걱정이야.</t>
-        </is>
-      </c>
-      <c r="F1062" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="G1062" s="6" t="inlineStr"/>
     </row>
     <row r="1063">
       <c r="A1063" s="4" t="inlineStr">
@@ -29258,7 +29258,7 @@
         <v>11</v>
       </c>
       <c r="C1063" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1063" s="4" t="inlineStr">
         <is>
@@ -29267,11 +29267,11 @@
       </c>
       <c r="E1063" s="5" t="inlineStr">
         <is>
-          <t>특히 처음 컨택하는 사람들은 대부분 "답장이 안 오면 어떡하지?"를 제일 무서워해.</t>
+          <t>그 마음은 정말 자연스러운 걱정이야.</t>
         </is>
       </c>
       <c r="F1063" s="4" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="G1063" s="6" t="inlineStr"/>
     </row>
@@ -29285,7 +29285,7 @@
         <v>11</v>
       </c>
       <c r="C1064" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1064" s="4" t="inlineStr">
         <is>
@@ -29294,11 +29294,11 @@
       </c>
       <c r="E1064" s="5" t="inlineStr">
         <is>
-          <t>그런데 하나 말해주고 싶은 게 있어.</t>
+          <t>특히 처음 컨택하는 사람들은 대부분 "답장이 안 오면 어떡하지?"를 제일 무서워해.</t>
         </is>
       </c>
       <c r="F1064" s="4" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G1064" s="6" t="inlineStr"/>
     </row>
@@ -29312,7 +29312,7 @@
         <v>11</v>
       </c>
       <c r="C1065" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1065" s="4" t="inlineStr">
         <is>
@@ -29321,11 +29321,11 @@
       </c>
       <c r="E1065" s="5" t="inlineStr">
         <is>
-          <t>답장이 안 오는 건 생각보다 흔한 일이고, 네 능력을 평가하는 결과가 아닌 경우가 많아.</t>
+          <t>그런데 하나 말해주고 싶은 게 있어.</t>
         </is>
       </c>
       <c r="F1065" s="4" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="G1065" s="6" t="inlineStr"/>
     </row>
@@ -29339,7 +29339,7 @@
         <v>11</v>
       </c>
       <c r="C1066" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1066" s="4" t="inlineStr">
         <is>
@@ -29348,11 +29348,11 @@
       </c>
       <c r="E1066" s="5" t="inlineStr">
         <is>
-          <t>예를 들어 교수님들은</t>
+          <t>답장이 안 오는 건 생각보다 흔한 일이고, 네 능력을 평가하는 결과가 아닌 경우가 많아.</t>
         </is>
       </c>
       <c r="F1066" s="4" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="G1066" s="6" t="inlineStr"/>
     </row>
@@ -29366,7 +29366,7 @@
         <v>11</v>
       </c>
       <c r="C1067" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1067" s="4" t="inlineStr">
         <is>
@@ -29375,11 +29375,11 @@
       </c>
       <c r="E1067" s="5" t="inlineStr">
         <is>
-          <t>학회 참석</t>
+          <t>예를 들어 교수님들은</t>
         </is>
       </c>
       <c r="F1067" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G1067" s="6" t="inlineStr"/>
     </row>
@@ -29393,7 +29393,7 @@
         <v>11</v>
       </c>
       <c r="C1068" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1068" s="4" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
       </c>
       <c r="E1068" s="5" t="inlineStr">
         <is>
-          <t>논문 마감</t>
+          <t>학회 참석</t>
         </is>
       </c>
       <c r="F1068" s="4" t="n">
@@ -29420,7 +29420,7 @@
         <v>11</v>
       </c>
       <c r="C1069" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1069" s="4" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
       </c>
       <c r="E1069" s="5" t="inlineStr">
         <is>
-          <t>해외 출장</t>
+          <t>논문 마감</t>
         </is>
       </c>
       <c r="F1069" s="4" t="n">
@@ -29447,7 +29447,7 @@
         <v>11</v>
       </c>
       <c r="C1070" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1070" s="4" t="inlineStr">
         <is>
@@ -29456,11 +29456,11 @@
       </c>
       <c r="E1070" s="5" t="inlineStr">
         <is>
-          <t>연구비 제안서</t>
+          <t>해외 출장</t>
         </is>
       </c>
       <c r="F1070" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1070" s="6" t="inlineStr"/>
     </row>
@@ -29474,7 +29474,7 @@
         <v>11</v>
       </c>
       <c r="C1071" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D1071" s="4" t="inlineStr">
         <is>
@@ -29483,11 +29483,11 @@
       </c>
       <c r="E1071" s="5" t="inlineStr">
         <is>
-          <t>학생 지도</t>
+          <t>연구비 제안서</t>
         </is>
       </c>
       <c r="F1071" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1071" s="6" t="inlineStr"/>
     </row>
@@ -29501,7 +29501,7 @@
         <v>11</v>
       </c>
       <c r="C1072" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D1072" s="4" t="inlineStr">
         <is>
@@ -29510,11 +29510,11 @@
       </c>
       <c r="E1072" s="5" t="inlineStr">
         <is>
-          <t>때문에 메일을 놓치는 경우가 정말 많아.</t>
+          <t>학생 지도</t>
         </is>
       </c>
       <c r="F1072" s="4" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G1072" s="6" t="inlineStr"/>
     </row>
@@ -29528,7 +29528,7 @@
         <v>11</v>
       </c>
       <c r="C1073" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1073" s="4" t="inlineStr">
         <is>
@@ -29537,11 +29537,11 @@
       </c>
       <c r="E1073" s="5" t="inlineStr">
         <is>
-          <t>실제로는 이런 경우가 많아.</t>
+          <t>때문에 메일을 놓치는 경우가 정말 많아.</t>
         </is>
       </c>
       <c r="F1073" s="4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G1073" s="6" t="inlineStr"/>
     </row>
@@ -29555,7 +29555,7 @@
         <v>11</v>
       </c>
       <c r="C1074" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1074" s="4" t="inlineStr">
         <is>
@@ -29564,11 +29564,11 @@
       </c>
       <c r="E1074" s="5" t="inlineStr">
         <is>
-          <t>학생 A 10명 컨택 → 2명 답장 학생 B 15명 컨택 → 5명 답장 학생 C 8명 컨택 → 0명 답장 → 1주일 뒤 다시 메일 → 면담 성사 이런 일은 흔하다.</t>
+          <t>실제로는 이런 경우가 많아.</t>
         </is>
       </c>
       <c r="F1074" s="4" t="n">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="G1074" s="6" t="inlineStr"/>
     </row>
@@ -29582,7 +29582,7 @@
         <v>11</v>
       </c>
       <c r="C1075" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D1075" s="4" t="inlineStr">
         <is>
@@ -29591,11 +29591,11 @@
       </c>
       <c r="E1075" s="5" t="inlineStr">
         <is>
-          <t>그래서 컨택은 "지원"이라기보다 "확률 게임"에 가까워.</t>
+          <t>학생 A 10명 컨택 → 2명 답장 학생 B 15명 컨택 → 5명 답장 학생 C 8명 컨택 → 0명 답장 → 1주일 뒤 다시 메일 → 면담 성사 이런 일은 흔하다.</t>
         </is>
       </c>
       <c r="F1075" s="4" t="n">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="G1075" s="6" t="inlineStr"/>
     </row>
@@ -29609,7 +29609,7 @@
         <v>11</v>
       </c>
       <c r="C1076" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1076" s="4" t="inlineStr">
         <is>
@@ -29618,11 +29618,11 @@
       </c>
       <c r="E1076" s="5" t="inlineStr">
         <is>
-          <t>예를 들어 한 명에게만 보내면</t>
+          <t>그래서 컨택은 "지원"이라기보다 "확률 게임"에 가까워.</t>
         </is>
       </c>
       <c r="F1076" s="4" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G1076" s="6" t="inlineStr"/>
     </row>
@@ -29636,20 +29636,20 @@
         <v>11</v>
       </c>
       <c r="C1077" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1077" s="4" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E1077" s="5" t="inlineStr">
+        <is>
+          <t>예를 들어 한 명에게만 보내면</t>
+        </is>
+      </c>
+      <c r="F1077" s="4" t="n">
         <v>16</v>
-      </c>
-      <c r="D1077" s="4" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E1077" s="5" t="inlineStr">
-        <is>
-          <t>1명 ↓ 답장 X ↓ 끝</t>
-        </is>
-      </c>
-      <c r="F1077" s="4" t="n">
-        <v>13</v>
       </c>
       <c r="G1077" s="6" t="inlineStr"/>
     </row>
@@ -29663,7 +29663,7 @@
         <v>11</v>
       </c>
       <c r="C1078" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D1078" s="4" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
       </c>
       <c r="E1078" s="5" t="inlineStr">
         <is>
-          <t>하지만 10명에게 보내면</t>
+          <t>1명 ↓ 답장 X ↓ 끝</t>
         </is>
       </c>
       <c r="F1078" s="4" t="n">
@@ -29690,7 +29690,7 @@
         <v>11</v>
       </c>
       <c r="C1079" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1079" s="4" t="inlineStr">
         <is>
@@ -29699,11 +29699,11 @@
       </c>
       <c r="E1079" s="5" t="inlineStr">
         <is>
-          <t>10명 ↓ 3명 답장 ↓ 1~2명 면담</t>
+          <t>하지만 10명에게 보내면</t>
         </is>
       </c>
       <c r="F1079" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G1079" s="6" t="inlineStr"/>
     </row>
@@ -29717,7 +29717,7 @@
         <v>11</v>
       </c>
       <c r="C1080" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1080" s="4" t="inlineStr">
         <is>
@@ -29726,11 +29726,11 @@
       </c>
       <c r="E1080" s="5" t="inlineStr">
         <is>
-          <t>이런 식으로 진행되는 경우가 많아.</t>
+          <t>10명 ↓ 3명 답장 ↓ 1~2명 면담</t>
         </is>
       </c>
       <c r="F1080" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G1080" s="6" t="inlineStr"/>
     </row>
@@ -29744,7 +29744,7 @@
         <v>11</v>
       </c>
       <c r="C1081" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D1081" s="4" t="inlineStr">
         <is>
@@ -29753,11 +29753,11 @@
       </c>
       <c r="E1081" s="5" t="inlineStr">
         <is>
-          <t>답장이 없으면 어떻게 해야 할까?</t>
+          <t>이런 식으로 진행되는 경우가 많아.</t>
         </is>
       </c>
       <c r="F1081" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1081" s="6" t="inlineStr"/>
     </row>
@@ -29771,7 +29771,7 @@
         <v>11</v>
       </c>
       <c r="C1082" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1082" s="4" t="inlineStr">
         <is>
@@ -29780,11 +29780,11 @@
       </c>
       <c r="E1082" s="5" t="inlineStr">
         <is>
-          <t>보통은</t>
+          <t>답장이 없으면 어떻게 해야 할까?</t>
         </is>
       </c>
       <c r="F1082" s="4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G1082" s="6" t="inlineStr"/>
     </row>
@@ -29798,7 +29798,7 @@
         <v>11</v>
       </c>
       <c r="C1083" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1083" s="4" t="inlineStr">
         <is>
@@ -29807,11 +29807,11 @@
       </c>
       <c r="E1083" s="5" t="inlineStr">
         <is>
-          <t>5~7일 정도 기다린 뒤</t>
+          <t>보통은</t>
         </is>
       </c>
       <c r="F1083" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G1083" s="6" t="inlineStr"/>
     </row>
@@ -29825,7 +29825,7 @@
         <v>11</v>
       </c>
       <c r="C1084" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D1084" s="4" t="inlineStr">
         <is>
@@ -29834,11 +29834,11 @@
       </c>
       <c r="E1084" s="5" t="inlineStr">
         <is>
-          <t>정중하게 한 번 더 메일을 보내면 된다.</t>
+          <t>5~7일 정도 기다린 뒤</t>
         </is>
       </c>
       <c r="F1084" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G1084" s="6" t="inlineStr"/>
     </row>
@@ -29852,7 +29852,7 @@
         <v>11</v>
       </c>
       <c r="C1085" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1085" s="4" t="inlineStr">
         <is>
@@ -29861,11 +29861,11 @@
       </c>
       <c r="E1085" s="5" t="inlineStr">
         <is>
-          <t>예를 들면 "안녕하세요, 지난주에 대학원 컨택 메일을 드렸던 ○○○입니다. 바쁘실 것 같아 다시 한번 메일드립니다."이 정도면 충분해.</t>
+          <t>정중하게 한 번 더 메일을 보내면 된다.</t>
         </is>
       </c>
       <c r="F1085" s="4" t="n">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="G1085" s="6" t="inlineStr"/>
     </row>
@@ -29879,7 +29879,7 @@
         <v>11</v>
       </c>
       <c r="C1086" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D1086" s="4" t="inlineStr">
         <is>
@@ -29888,11 +29888,11 @@
       </c>
       <c r="E1086" s="5" t="inlineStr">
         <is>
-          <t>그래도 답이 없다면 그 연구실은 일단 넘기고 다른 곳에 집중하면 돼.</t>
+          <t>예를 들면 "안녕하세요, 지난주에 대학원 컨택 메일을 드렸던 ○○○입니다. 바쁘실 것 같아 다시 한번 메일드립니다."이 정도면 충분해.</t>
         </is>
       </c>
       <c r="F1086" s="4" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="G1086" s="6" t="inlineStr"/>
     </row>
@@ -29906,7 +29906,7 @@
         <v>11</v>
       </c>
       <c r="C1087" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D1087" s="4" t="inlineStr">
         <is>
@@ -29915,11 +29915,11 @@
       </c>
       <c r="E1087" s="5" t="inlineStr">
         <is>
-          <t>그리고 하나 중요한 것.</t>
+          <t>그래도 답이 없다면 그 연구실은 일단 넘기고 다른 곳에 집중하면 돼.</t>
         </is>
       </c>
       <c r="F1087" s="4" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G1087" s="6" t="inlineStr"/>
     </row>
@@ -29933,7 +29933,7 @@
         <v>11</v>
       </c>
       <c r="C1088" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1088" s="4" t="inlineStr">
         <is>
@@ -29942,11 +29942,11 @@
       </c>
       <c r="E1088" s="5" t="inlineStr">
         <is>
-          <t>너는 지금 "답장이 안 오면?"을 걱정하고 있는데, 나는 오히려 "한 명에게만 보내는 것"을 더 걱정해.</t>
+          <t>그리고 하나 중요한 것.</t>
         </is>
       </c>
       <c r="F1088" s="4" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="G1088" s="6" t="inlineStr"/>
     </row>
@@ -29960,7 +29960,7 @@
         <v>11</v>
       </c>
       <c r="C1089" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D1089" s="4" t="inlineStr">
         <is>
@@ -29969,11 +29969,11 @@
       </c>
       <c r="E1089" s="5" t="inlineStr">
         <is>
-          <t>컨택은 원래 여러 연구실에 하는 거야.</t>
+          <t>너는 지금 "답장이 안 오면?"을 걱정하고 있는데, 나는 오히려 "한 명에게만 보내는 것"을 더 걱정해.</t>
         </is>
       </c>
       <c r="F1089" s="4" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G1089" s="6" t="inlineStr"/>
     </row>
@@ -29987,7 +29987,7 @@
         <v>11</v>
       </c>
       <c r="C1090" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1090" s="4" t="inlineStr">
         <is>
@@ -29996,11 +29996,11 @@
       </c>
       <c r="E1090" s="5" t="inlineStr">
         <is>
-          <t>교수님들도 그걸 알고 있어.</t>
+          <t>컨택은 원래 여러 연구실에 하는 거야.</t>
         </is>
       </c>
       <c r="F1090" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G1090" s="6" t="inlineStr"/>
     </row>
@@ -30014,7 +30014,7 @@
         <v>11</v>
       </c>
       <c r="C1091" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1091" s="4" t="inlineStr">
         <is>
@@ -30023,11 +30023,11 @@
       </c>
       <c r="E1091" s="5" t="inlineStr">
         <is>
-          <t>지금 너의 강점도 생각해보자.</t>
+          <t>교수님들도 그걸 알고 있어.</t>
         </is>
       </c>
       <c r="F1091" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1091" s="6" t="inlineStr"/>
     </row>
@@ -30041,7 +30041,7 @@
         <v>11</v>
       </c>
       <c r="C1092" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1092" s="4" t="inlineStr">
         <is>
@@ -30050,11 +30050,11 @@
       </c>
       <c r="E1092" s="5" t="inlineStr">
         <is>
-          <t>너는</t>
+          <t>지금 너의 강점도 생각해보자.</t>
         </is>
       </c>
       <c r="F1092" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G1092" s="6" t="inlineStr"/>
     </row>
@@ -30068,7 +30068,7 @@
         <v>11</v>
       </c>
       <c r="C1093" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D1093" s="4" t="inlineStr">
         <is>
@@ -30077,11 +30077,11 @@
       </c>
       <c r="E1093" s="5" t="inlineStr">
         <is>
-          <t>학부 연구 경험이 있고</t>
+          <t>너는</t>
         </is>
       </c>
       <c r="F1093" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G1093" s="6" t="inlineStr"/>
     </row>
@@ -30095,7 +30095,7 @@
         <v>11</v>
       </c>
       <c r="C1094" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D1094" s="4" t="inlineStr">
         <is>
@@ -30104,11 +30104,11 @@
       </c>
       <c r="E1094" s="5" t="inlineStr">
         <is>
-          <t>프로젝트 경험이 있고</t>
+          <t>학부 연구 경험이 있고</t>
         </is>
       </c>
       <c r="F1094" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G1094" s="6" t="inlineStr"/>
     </row>
@@ -30122,7 +30122,7 @@
         <v>11</v>
       </c>
       <c r="C1095" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D1095" s="4" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="E1095" s="5" t="inlineStr">
         <is>
-          <t>CV도 준비하고 있고</t>
+          <t>프로젝트 경험이 있고</t>
         </is>
       </c>
       <c r="F1095" s="4" t="n">
@@ -30149,7 +30149,7 @@
         <v>11</v>
       </c>
       <c r="C1096" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1096" s="4" t="inlineStr">
         <is>
@@ -30158,11 +30158,11 @@
       </c>
       <c r="E1096" s="5" t="inlineStr">
         <is>
-          <t>대학원을 진지하게 고민하고 있어.</t>
+          <t>CV도 준비하고 있고</t>
         </is>
       </c>
       <c r="F1096" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G1096" s="6" t="inlineStr"/>
     </row>
@@ -30176,7 +30176,7 @@
         <v>11</v>
       </c>
       <c r="C1097" s="4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D1097" s="4" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="E1097" s="5" t="inlineStr">
         <is>
-          <t>이건 컨택할 때 분명한 장점이야.</t>
+          <t>대학원을 진지하게 고민하고 있어.</t>
         </is>
       </c>
       <c r="F1097" s="4" t="n">
@@ -30203,7 +30203,7 @@
         <v>11</v>
       </c>
       <c r="C1098" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1098" s="4" t="inlineStr">
         <is>
@@ -30212,11 +30212,11 @@
       </c>
       <c r="E1098" s="5" t="inlineStr">
         <is>
-          <t>물론 명문 연구실은 경쟁이 치열해서 답장이 없을 수도 있지만, 그게 "너는 부족하다"는 뜻은 아니야.</t>
+          <t>이건 컨택할 때 분명한 장점이야.</t>
         </is>
       </c>
       <c r="F1098" s="4" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="G1098" s="6" t="inlineStr"/>
     </row>
@@ -30230,7 +30230,7 @@
         <v>11</v>
       </c>
       <c r="C1099" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1099" s="4" t="inlineStr">
         <is>
@@ -30239,11 +30239,11 @@
       </c>
       <c r="E1099" s="5" t="inlineStr">
         <is>
-          <t>내가 하나 제안할게.</t>
+          <t>물론 명문 연구실은 경쟁이 치열해서 답장이 없을 수도 있지만, 그게 "너는 부족하다"는 뜻은 아니야.</t>
         </is>
       </c>
       <c r="F1099" s="4" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="G1099" s="6" t="inlineStr"/>
     </row>
@@ -30257,7 +30257,7 @@
         <v>11</v>
       </c>
       <c r="C1100" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1100" s="4" t="inlineStr">
         <is>
@@ -30266,11 +30266,11 @@
       </c>
       <c r="E1100" s="5" t="inlineStr">
         <is>
-          <t>교수님을 세 그룹으로 나눠서 컨택하는 전략을 추천해.</t>
+          <t>내가 하나 제안할게.</t>
         </is>
       </c>
       <c r="F1100" s="4" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G1100" s="6" t="inlineStr"/>
     </row>
@@ -30284,7 +30284,7 @@
         <v>11</v>
       </c>
       <c r="C1101" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1101" s="4" t="inlineStr">
         <is>
@@ -30293,11 +30293,11 @@
       </c>
       <c r="E1101" s="5" t="inlineStr">
         <is>
-          <t>도전: 꼭 가고 싶은 연구실 3~5곳</t>
+          <t>교수님을 세 그룹으로 나눠서 컨택하는 전략을 추천해.</t>
         </is>
       </c>
       <c r="F1101" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G1101" s="6" t="inlineStr"/>
     </row>
@@ -30311,7 +30311,7 @@
         <v>11</v>
       </c>
       <c r="C1102" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D1102" s="4" t="inlineStr">
         <is>
@@ -30320,11 +30320,11 @@
       </c>
       <c r="E1102" s="5" t="inlineStr">
         <is>
-          <t>적정: 현재 연구 경험으로 충분히 경쟁 가능한 곳 5~7곳</t>
+          <t>도전: 꼭 가고 싶은 연구실 3~5곳</t>
         </is>
       </c>
       <c r="F1102" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G1102" s="6" t="inlineStr"/>
     </row>
@@ -30338,7 +30338,7 @@
         <v>11</v>
       </c>
       <c r="C1103" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D1103" s="4" t="inlineStr">
         <is>
@@ -30347,11 +30347,11 @@
       </c>
       <c r="E1103" s="5" t="inlineStr">
         <is>
-          <t>안정: 비교적 가능성이 높은 곳 3~5곳</t>
+          <t>적정: 현재 연구 경험으로 충분히 경쟁 가능한 곳 5~7곳</t>
         </is>
       </c>
       <c r="F1103" s="4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G1103" s="6" t="inlineStr"/>
     </row>
@@ -30365,7 +30365,7 @@
         <v>11</v>
       </c>
       <c r="C1104" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D1104" s="4" t="inlineStr">
         <is>
@@ -30374,11 +30374,11 @@
       </c>
       <c r="E1104" s="5" t="inlineStr">
         <is>
-          <t>이렇게 하면 한 곳에서 답장이 없더라도 다음 기회가 계속 남아 있어서 심리적으로도 훨씬 부담이 적어져.</t>
+          <t>안정: 비교적 가능성이 높은 곳 3~5곳</t>
         </is>
       </c>
       <c r="F1104" s="4" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="G1104" s="6" t="inlineStr"/>
     </row>
@@ -30392,7 +30392,7 @@
         <v>11</v>
       </c>
       <c r="C1105" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D1105" s="4" t="inlineStr">
         <is>
@@ -30401,11 +30401,11 @@
       </c>
       <c r="E1105" s="5" t="inlineStr">
         <is>
-          <t>그리고 한 가지는 꼭 기억했으면 좋겠어.</t>
+          <t>이렇게 하면 한 곳에서 답장이 없더라도 다음 기회가 계속 남아 있어서 심리적으로도 훨씬 부담이 적어져.</t>
         </is>
       </c>
       <c r="F1105" s="4" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="G1105" s="6" t="inlineStr"/>
     </row>
@@ -30419,7 +30419,7 @@
         <v>11</v>
       </c>
       <c r="C1106" s="4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1106" s="4" t="inlineStr">
         <is>
@@ -30428,11 +30428,11 @@
       </c>
       <c r="E1106" s="5" t="inlineStr">
         <is>
-          <t>컨택 메일을 보내는 순간부터는 결과를 통제할 수 없어.</t>
+          <t>그리고 한 가지는 꼭 기억했으면 좋겠어.</t>
         </is>
       </c>
       <c r="F1106" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G1106" s="6" t="inlineStr"/>
     </row>
@@ -30446,7 +30446,7 @@
         <v>11</v>
       </c>
       <c r="C1107" s="4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D1107" s="4" t="inlineStr">
         <is>
@@ -30455,11 +30455,11 @@
       </c>
       <c r="E1107" s="5" t="inlineStr">
         <is>
-          <t>통제할 수 있는 건</t>
+          <t>컨택 메일을 보내는 순간부터는 결과를 통제할 수 없어.</t>
         </is>
       </c>
       <c r="F1107" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G1107" s="6" t="inlineStr"/>
     </row>
@@ -30473,7 +30473,7 @@
         <v>11</v>
       </c>
       <c r="C1108" s="4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D1108" s="4" t="inlineStr">
         <is>
@@ -30482,11 +30482,11 @@
       </c>
       <c r="E1108" s="5" t="inlineStr">
         <is>
-          <t>좋은 CV를 준비하는 것,</t>
+          <t>통제할 수 있는 건</t>
         </is>
       </c>
       <c r="F1108" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G1108" s="6" t="inlineStr"/>
     </row>
@@ -30500,7 +30500,7 @@
         <v>11</v>
       </c>
       <c r="C1109" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D1109" s="4" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
       </c>
       <c r="E1109" s="5" t="inlineStr">
         <is>
-          <t>연구실을 잘 조사하는 것,</t>
+          <t>좋은 CV를 준비하는 것,</t>
         </is>
       </c>
       <c r="F1109" s="4" t="n">
@@ -30527,7 +30527,7 @@
         <v>11</v>
       </c>
       <c r="C1110" s="4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D1110" s="4" t="inlineStr">
         <is>
@@ -30536,11 +30536,11 @@
       </c>
       <c r="E1110" s="5" t="inlineStr">
         <is>
-          <t>메일을 정성껏 쓰는 것,</t>
+          <t>연구실을 잘 조사하는 것,</t>
         </is>
       </c>
       <c r="F1110" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G1110" s="6" t="inlineStr"/>
     </row>
@@ -30554,7 +30554,7 @@
         <v>11</v>
       </c>
       <c r="C1111" s="4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D1111" s="4" t="inlineStr">
         <is>
@@ -30563,11 +30563,11 @@
       </c>
       <c r="E1111" s="5" t="inlineStr">
         <is>
-          <t>여러 곳에 지원하는 것</t>
+          <t>메일을 정성껏 쓰는 것,</t>
         </is>
       </c>
       <c r="F1111" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1111" s="6" t="inlineStr"/>
     </row>
@@ -30581,7 +30581,7 @@
         <v>11</v>
       </c>
       <c r="C1112" s="4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1112" s="4" t="inlineStr">
         <is>
@@ -30590,11 +30590,11 @@
       </c>
       <c r="E1112" s="5" t="inlineStr">
         <is>
-          <t>이 네 가지야.</t>
+          <t>여러 곳에 지원하는 것</t>
         </is>
       </c>
       <c r="F1112" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G1112" s="6" t="inlineStr"/>
     </row>
@@ -30608,7 +30608,7 @@
         <v>11</v>
       </c>
       <c r="C1113" s="4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D1113" s="4" t="inlineStr">
         <is>
@@ -30617,11 +30617,11 @@
       </c>
       <c r="E1113" s="5" t="inlineStr">
         <is>
-          <t>그 부분을 잘 준비했다면, 답장이 늦거나 오지 않는 것은 너무 개인적으로 받아들이지 않았으면 좋겠어.</t>
+          <t>이 네 가지야.</t>
         </is>
       </c>
       <c r="F1113" s="4" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="G1113" s="6" t="inlineStr"/>
     </row>
@@ -30635,82 +30635,82 @@
         <v>11</v>
       </c>
       <c r="C1114" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="D1114" s="4" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E1114" s="5" t="inlineStr">
+        <is>
+          <t>그 부분을 잘 준비했다면, 답장이 늦거나 오지 않는 것은 너무 개인적으로 받아들이지 않았으면 좋겠어.</t>
+        </is>
+      </c>
+      <c r="F1114" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="G1114" s="6" t="inlineStr"/>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="4" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B1115" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1115" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="D1114" s="4" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E1114" s="5" t="inlineStr">
+      <c r="D1115" s="4" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E1115" s="5" t="inlineStr">
         <is>
           <t>많은 대학원생들이 비슷한 과정을 거쳐 원하는 연구실을 찾았으니까.</t>
         </is>
       </c>
-      <c r="F1114" s="4" t="n">
+      <c r="F1115" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="G1114" s="6" t="inlineStr"/>
-    </row>
-    <row r="1115">
-      <c r="A1115" s="2" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="B1115" s="2" t="n">
+      <c r="G1115" s="6" t="inlineStr"/>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="2" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B1116" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="C1115" s="2" t="inlineStr">
+      <c r="C1116" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D1115" s="2" t="inlineStr">
+      <c r="D1116" s="2" t="inlineStr">
         <is>
           <t>Prompt</t>
         </is>
       </c>
-      <c r="E1115" s="3" t="inlineStr">
+      <c r="E1116" s="3" t="inlineStr">
         <is>
           <t>기업 학연과정? 계약학과 이런 것도 차장줄 수 있어 ?</t>
         </is>
       </c>
-      <c r="F1115" s="2" t="n">
+      <c r="F1116" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G1115" s="2" t="inlineStr">
+      <c r="G1116" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="1116">
-      <c r="A1116" s="7" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="B1116" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C1116" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1116" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E1116" s="8" t="inlineStr">
-        <is>
-          <t>응.</t>
-        </is>
-      </c>
-      <c r="F1116" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1116" s="6" t="inlineStr"/>
     </row>
     <row r="1117">
       <c r="A1117" s="7" t="inlineStr">
@@ -30722,20 +30722,20 @@
         <v>12</v>
       </c>
       <c r="C1117" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1117" s="7" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E1117" s="8" t="inlineStr">
+        <is>
+          <t>응.</t>
+        </is>
+      </c>
+      <c r="F1117" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="D1117" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E1117" s="8" t="inlineStr">
-        <is>
-          <t>오히려 너라면 일반 대학원뿐 아니라 기업 연계 과정도 꼭 같이 봤으면 좋겠어.</t>
-        </is>
-      </c>
-      <c r="F1117" s="7" t="n">
-        <v>43</v>
       </c>
       <c r="G1117" s="6" t="inlineStr"/>
     </row>
@@ -30749,7 +30749,7 @@
         <v>12</v>
       </c>
       <c r="C1118" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1118" s="7" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="E1118" s="8" t="inlineStr">
         <is>
-          <t>왜냐하면 너는 아직 "박사를 할지" "기업 연구직으로 갈지" 정하지 못했잖아.</t>
+          <t>오히려 너라면 일반 대학원뿐 아니라 기업 연계 과정도 꼭 같이 봤으면 좋겠어.</t>
         </is>
       </c>
       <c r="F1118" s="7" t="n">
@@ -30776,7 +30776,7 @@
         <v>12</v>
       </c>
       <c r="C1119" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1119" s="7" t="inlineStr">
         <is>
@@ -30785,11 +30785,11 @@
       </c>
       <c r="E1119" s="8" t="inlineStr">
         <is>
-          <t>그럼 선택지를 넓게 가져가는 게 좋아.</t>
+          <t>왜냐하면 너는 아직 "박사를 할지" "기업 연구직으로 갈지" 정하지 못했잖아.</t>
         </is>
       </c>
       <c r="F1119" s="7" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="G1119" s="6" t="inlineStr"/>
     </row>
@@ -30803,7 +30803,7 @@
         <v>12</v>
       </c>
       <c r="C1120" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1120" s="7" t="inlineStr">
         <is>
@@ -30812,11 +30812,11 @@
       </c>
       <c r="E1120" s="8" t="inlineStr">
         <is>
-          <t>크게 4가지가 있어</t>
+          <t>그럼 선택지를 넓게 가져가는 게 좋아.</t>
         </is>
       </c>
       <c r="F1120" s="7" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G1120" s="6" t="inlineStr"/>
     </row>
@@ -30830,7 +30830,7 @@
         <v>12</v>
       </c>
       <c r="C1121" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1121" s="7" t="inlineStr">
         <is>
@@ -30839,11 +30839,11 @@
       </c>
       <c r="E1121" s="8" t="inlineStr">
         <is>
-          <t>① 일반 대학원 (가장 일반적)</t>
+          <t>크게 4가지가 있어</t>
         </is>
       </c>
       <c r="F1121" s="7" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G1121" s="6" t="inlineStr"/>
     </row>
@@ -30857,7 +30857,7 @@
         <v>12</v>
       </c>
       <c r="C1122" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1122" s="7" t="inlineStr">
         <is>
@@ -30866,11 +30866,11 @@
       </c>
       <c r="E1122" s="8" t="inlineStr">
         <is>
-          <t>석사 ↓ 취업 or 박사</t>
+          <t>① 일반 대학원 (가장 일반적)</t>
         </is>
       </c>
       <c r="F1122" s="7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G1122" s="6" t="inlineStr"/>
     </row>
@@ -30884,7 +30884,7 @@
         <v>12</v>
       </c>
       <c r="C1123" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1123" s="7" t="inlineStr">
         <is>
@@ -30893,11 +30893,11 @@
       </c>
       <c r="E1123" s="8" t="inlineStr">
         <is>
-          <t>장점</t>
+          <t>석사 ↓ 취업 or 박사</t>
         </is>
       </c>
       <c r="F1123" s="7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G1123" s="6" t="inlineStr"/>
     </row>
@@ -30911,7 +30911,7 @@
         <v>12</v>
       </c>
       <c r="C1124" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1124" s="7" t="inlineStr">
         <is>
@@ -30920,11 +30920,11 @@
       </c>
       <c r="E1124" s="8" t="inlineStr">
         <is>
-          <t>연구 자유도가 높다.</t>
+          <t>장점</t>
         </is>
       </c>
       <c r="F1124" s="7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G1124" s="6" t="inlineStr"/>
     </row>
@@ -30938,7 +30938,7 @@
         <v>12</v>
       </c>
       <c r="C1125" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D1125" s="7" t="inlineStr">
         <is>
@@ -30947,11 +30947,11 @@
       </c>
       <c r="E1125" s="8" t="inlineStr">
         <is>
-          <t>교수님 연구를 깊게 할 수 있다.</t>
+          <t>연구 자유도가 높다.</t>
         </is>
       </c>
       <c r="F1125" s="7" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G1125" s="6" t="inlineStr"/>
     </row>
@@ -30965,7 +30965,7 @@
         <v>12</v>
       </c>
       <c r="C1126" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D1126" s="7" t="inlineStr">
         <is>
@@ -30974,11 +30974,11 @@
       </c>
       <c r="E1126" s="8" t="inlineStr">
         <is>
-          <t>박사 진학하기 좋다.</t>
+          <t>교수님 연구를 깊게 할 수 있다.</t>
         </is>
       </c>
       <c r="F1126" s="7" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G1126" s="6" t="inlineStr"/>
     </row>
@@ -30992,7 +30992,7 @@
         <v>12</v>
       </c>
       <c r="C1127" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1127" s="7" t="inlineStr">
         <is>
@@ -31001,11 +31001,11 @@
       </c>
       <c r="E1127" s="8" t="inlineStr">
         <is>
-          <t>단점</t>
+          <t>박사 진학하기 좋다.</t>
         </is>
       </c>
       <c r="F1127" s="7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G1127" s="6" t="inlineStr"/>
     </row>
@@ -31019,7 +31019,7 @@
         <v>12</v>
       </c>
       <c r="C1128" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1128" s="7" t="inlineStr">
         <is>
@@ -31028,11 +31028,11 @@
       </c>
       <c r="E1128" s="8" t="inlineStr">
         <is>
-          <t>등록금</t>
+          <t>단점</t>
         </is>
       </c>
       <c r="F1128" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1128" s="6" t="inlineStr"/>
     </row>
@@ -31046,7 +31046,7 @@
         <v>12</v>
       </c>
       <c r="C1129" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D1129" s="7" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
       </c>
       <c r="E1129" s="8" t="inlineStr">
         <is>
-          <t>생활비</t>
+          <t>등록금</t>
         </is>
       </c>
       <c r="F1129" s="7" t="n">
@@ -31073,7 +31073,7 @@
         <v>12</v>
       </c>
       <c r="C1130" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1130" s="7" t="inlineStr">
         <is>
@@ -31082,11 +31082,11 @@
       </c>
       <c r="E1130" s="8" t="inlineStr">
         <is>
-          <t>취업은 본인이 준비해야 한다.</t>
+          <t>생활비</t>
         </is>
       </c>
       <c r="F1130" s="7" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G1130" s="6" t="inlineStr"/>
     </row>
@@ -31100,20 +31100,20 @@
         <v>12</v>
       </c>
       <c r="C1131" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1131" s="7" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E1131" s="8" t="inlineStr">
+        <is>
+          <t>취업은 본인이 준비해야 한다.</t>
+        </is>
+      </c>
+      <c r="F1131" s="7" t="n">
         <v>16</v>
-      </c>
-      <c r="D1131" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E1131" s="8" t="inlineStr">
-        <is>
-          <t>추천도 ⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="F1131" s="7" t="n">
-        <v>9</v>
       </c>
       <c r="G1131" s="6" t="inlineStr"/>
     </row>
@@ -31127,7 +31127,7 @@
         <v>12</v>
       </c>
       <c r="C1132" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D1132" s="7" t="inlineStr">
         <is>
@@ -31136,11 +31136,11 @@
       </c>
       <c r="E1132" s="8" t="inlineStr">
         <is>
-          <t>② 기업 학연과정 (내가 꽤 추천)</t>
+          <t>추천도 ⭐⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="F1132" s="7" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G1132" s="6" t="inlineStr"/>
     </row>
@@ -31154,7 +31154,7 @@
         <v>12</v>
       </c>
       <c r="C1133" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1133" s="7" t="inlineStr">
         <is>
@@ -31163,11 +31163,11 @@
       </c>
       <c r="E1133" s="8" t="inlineStr">
         <is>
-          <t>예를 들면</t>
+          <t>② 기업 학연과정 (내가 꽤 추천)</t>
         </is>
       </c>
       <c r="F1133" s="7" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G1133" s="6" t="inlineStr"/>
     </row>
@@ -31181,7 +31181,7 @@
         <v>12</v>
       </c>
       <c r="C1134" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1134" s="7" t="inlineStr">
         <is>
@@ -31190,11 +31190,11 @@
       </c>
       <c r="E1134" s="8" t="inlineStr">
         <is>
-          <t>ETRI</t>
+          <t>예를 들면</t>
         </is>
       </c>
       <c r="F1134" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1134" s="6" t="inlineStr"/>
     </row>
@@ -31208,7 +31208,7 @@
         <v>12</v>
       </c>
       <c r="C1135" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D1135" s="7" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
       </c>
       <c r="E1135" s="8" t="inlineStr">
         <is>
-          <t>KETI</t>
+          <t>ETRI</t>
         </is>
       </c>
       <c r="F1135" s="7" t="n">
@@ -31235,7 +31235,7 @@
         <v>12</v>
       </c>
       <c r="C1136" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1136" s="7" t="inlineStr">
         <is>
@@ -31244,11 +31244,11 @@
       </c>
       <c r="E1136" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>KETI</t>
         </is>
       </c>
       <c r="F1136" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1136" s="6" t="inlineStr"/>
     </row>
@@ -31262,7 +31262,7 @@
         <v>12</v>
       </c>
       <c r="C1137" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1137" s="7" t="inlineStr">
         <is>
@@ -31271,11 +31271,11 @@
       </c>
       <c r="E1137" s="8" t="inlineStr">
         <is>
-          <t>현대자동차</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="F1137" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1137" s="6" t="inlineStr"/>
     </row>
@@ -31289,7 +31289,7 @@
         <v>12</v>
       </c>
       <c r="C1138" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D1138" s="7" t="inlineStr">
         <is>
@@ -31298,11 +31298,11 @@
       </c>
       <c r="E1138" s="8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대자동차</t>
         </is>
       </c>
       <c r="F1138" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1138" s="6" t="inlineStr"/>
     </row>
@@ -31316,7 +31316,7 @@
         <v>12</v>
       </c>
       <c r="C1139" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1139" s="7" t="inlineStr">
         <is>
@@ -31325,11 +31325,11 @@
       </c>
       <c r="E1139" s="8" t="inlineStr">
         <is>
-          <t>LG AI연구원</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="F1139" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1139" s="6" t="inlineStr"/>
     </row>
@@ -31343,7 +31343,7 @@
         <v>12</v>
       </c>
       <c r="C1140" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D1140" s="7" t="inlineStr">
         <is>
@@ -31352,11 +31352,11 @@
       </c>
       <c r="E1140" s="8" t="inlineStr">
         <is>
-          <t>한국생산기술연구원(KITECH)</t>
+          <t>LG AI연구원</t>
         </is>
       </c>
       <c r="F1140" s="7" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G1140" s="6" t="inlineStr"/>
     </row>
@@ -31370,7 +31370,7 @@
         <v>12</v>
       </c>
       <c r="C1141" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D1141" s="7" t="inlineStr">
         <is>
@@ -31379,11 +31379,11 @@
       </c>
       <c r="E1141" s="8" t="inlineStr">
         <is>
-          <t>등과 대학이 같이 운영하는 과정이야.</t>
+          <t>한국생산기술연구원(KITECH)</t>
         </is>
       </c>
       <c r="F1141" s="7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G1141" s="6" t="inlineStr"/>
     </row>
@@ -31397,7 +31397,7 @@
         <v>12</v>
       </c>
       <c r="C1142" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1142" s="7" t="inlineStr">
         <is>
@@ -31406,11 +31406,11 @@
       </c>
       <c r="E1142" s="8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>등과 대학이 같이 운영하는 과정이야.</t>
         </is>
       </c>
       <c r="F1142" s="7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G1142" s="6" t="inlineStr"/>
     </row>
@@ -31424,7 +31424,7 @@
         <v>12</v>
       </c>
       <c r="C1143" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D1143" s="7" t="inlineStr">
         <is>
@@ -31433,11 +31433,11 @@
       </c>
       <c r="E1143" s="8" t="inlineStr">
         <is>
-          <t>대학원 + 기업/연구소</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F1143" s="7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G1143" s="6" t="inlineStr"/>
     </row>
@@ -31451,7 +31451,7 @@
         <v>12</v>
       </c>
       <c r="C1144" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1144" s="7" t="inlineStr">
         <is>
@@ -31460,11 +31460,11 @@
       </c>
       <c r="E1144" s="8" t="inlineStr">
         <is>
-          <t>를 같이 다닌다.</t>
+          <t>대학원 + 기업/연구소</t>
         </is>
       </c>
       <c r="F1144" s="7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G1144" s="6" t="inlineStr"/>
     </row>
@@ -31478,7 +31478,7 @@
         <v>12</v>
       </c>
       <c r="C1145" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1145" s="7" t="inlineStr">
         <is>
@@ -31487,11 +31487,11 @@
       </c>
       <c r="E1145" s="8" t="inlineStr">
         <is>
-          <t>장점 ✅ 연구도 하고 ✅ 기업도 경험한다.</t>
+          <t>를 같이 다닌다.</t>
         </is>
       </c>
       <c r="F1145" s="7" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G1145" s="6" t="inlineStr"/>
     </row>
@@ -31505,7 +31505,7 @@
         <v>12</v>
       </c>
       <c r="C1146" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1146" s="7" t="inlineStr">
         <is>
@@ -31514,11 +31514,11 @@
       </c>
       <c r="E1146" s="8" t="inlineStr">
         <is>
-          <t>논문도 쓰고 실무도 한다.</t>
+          <t>장점 ✅ 연구도 하고 ✅ 기업도 경험한다.</t>
         </is>
       </c>
       <c r="F1146" s="7" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G1146" s="6" t="inlineStr"/>
     </row>
@@ -31532,7 +31532,7 @@
         <v>12</v>
       </c>
       <c r="C1147" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D1147" s="7" t="inlineStr">
         <is>
@@ -31541,11 +31541,11 @@
       </c>
       <c r="E1147" s="8" t="inlineStr">
         <is>
-          <t>너처럼 "산업 적용" 관심 있는 사람에게 정말 좋다.</t>
+          <t>논문도 쓰고 실무도 한다.</t>
         </is>
       </c>
       <c r="F1147" s="7" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G1147" s="6" t="inlineStr"/>
     </row>
@@ -31559,7 +31559,7 @@
         <v>12</v>
       </c>
       <c r="C1148" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D1148" s="7" t="inlineStr">
         <is>
@@ -31568,11 +31568,11 @@
       </c>
       <c r="E1148" s="8" t="inlineStr">
         <is>
-          <t>③ 계약학과</t>
+          <t>너처럼 "산업 적용" 관심 있는 사람에게 정말 좋다.</t>
         </is>
       </c>
       <c r="F1148" s="7" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G1148" s="6" t="inlineStr"/>
     </row>
@@ -31586,7 +31586,7 @@
         <v>12</v>
       </c>
       <c r="C1149" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D1149" s="7" t="inlineStr">
         <is>
@@ -31595,11 +31595,11 @@
       </c>
       <c r="E1149" s="8" t="inlineStr">
         <is>
-          <t>이건 조금 다르다.</t>
+          <t>③ 계약학과</t>
         </is>
       </c>
       <c r="F1149" s="7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G1149" s="6" t="inlineStr"/>
     </row>
@@ -31613,7 +31613,7 @@
         <v>12</v>
       </c>
       <c r="C1150" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1150" s="7" t="inlineStr">
         <is>
@@ -31622,11 +31622,11 @@
       </c>
       <c r="E1150" s="8" t="inlineStr">
         <is>
-          <t>예를 들면 삼성 계약학과 현대 계약학과 SK 계약학과 LG 계약학과 등이다.</t>
+          <t>이건 조금 다르다.</t>
         </is>
       </c>
       <c r="F1150" s="7" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="G1150" s="6" t="inlineStr"/>
     </row>
@@ -31640,7 +31640,7 @@
         <v>12</v>
       </c>
       <c r="C1151" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D1151" s="7" t="inlineStr">
         <is>
@@ -31649,11 +31649,11 @@
       </c>
       <c r="E1151" s="8" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>예를 들면 삼성 계약학과 현대 계약학과 SK 계약학과 LG 계약학과 등이다.</t>
         </is>
       </c>
       <c r="F1151" s="7" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="G1151" s="6" t="inlineStr"/>
     </row>
@@ -31667,7 +31667,7 @@
         <v>12</v>
       </c>
       <c r="C1152" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1152" s="7" t="inlineStr">
         <is>
@@ -31676,11 +31676,11 @@
       </c>
       <c r="E1152" s="8" t="inlineStr">
         <is>
-          <t>입학 ↓ 장학금 ↓ 졸업 ↓ 회사 입사</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="F1152" s="7" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G1152" s="6" t="inlineStr"/>
     </row>
@@ -31694,7 +31694,7 @@
         <v>12</v>
       </c>
       <c r="C1153" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1153" s="7" t="inlineStr">
         <is>
@@ -31703,11 +31703,11 @@
       </c>
       <c r="E1153" s="8" t="inlineStr">
         <is>
-          <t>형태다.</t>
+          <t>입학 ↓ 장학금 ↓ 졸업 ↓ 회사 입사</t>
         </is>
       </c>
       <c r="F1153" s="7" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G1153" s="6" t="inlineStr"/>
     </row>
@@ -31721,7 +31721,7 @@
         <v>12</v>
       </c>
       <c r="C1154" s="7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1154" s="7" t="inlineStr">
         <is>
@@ -31730,11 +31730,11 @@
       </c>
       <c r="E1154" s="8" t="inlineStr">
         <is>
-          <t>장점</t>
+          <t>형태다.</t>
         </is>
       </c>
       <c r="F1154" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1154" s="6" t="inlineStr"/>
     </row>
@@ -31748,7 +31748,7 @@
         <v>12</v>
       </c>
       <c r="C1155" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1155" s="7" t="inlineStr">
         <is>
@@ -31757,11 +31757,11 @@
       </c>
       <c r="E1155" s="8" t="inlineStr">
         <is>
-          <t>등록금 거의 지원</t>
+          <t>장점</t>
         </is>
       </c>
       <c r="F1155" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G1155" s="6" t="inlineStr"/>
     </row>
@@ -31775,7 +31775,7 @@
         <v>12</v>
       </c>
       <c r="C1156" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D1156" s="7" t="inlineStr">
         <is>
@@ -31784,11 +31784,11 @@
       </c>
       <c r="E1156" s="8" t="inlineStr">
         <is>
-          <t>생활비 지원인 경우도 있음</t>
+          <t>등록금 거의 지원</t>
         </is>
       </c>
       <c r="F1156" s="7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G1156" s="6" t="inlineStr"/>
     </row>
@@ -31802,7 +31802,7 @@
         <v>12</v>
       </c>
       <c r="C1157" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D1157" s="7" t="inlineStr">
         <is>
@@ -31811,11 +31811,11 @@
       </c>
       <c r="E1157" s="8" t="inlineStr">
         <is>
-          <t>취업이 거의 연결됨</t>
+          <t>생활비 지원인 경우도 있음</t>
         </is>
       </c>
       <c r="F1157" s="7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G1157" s="6" t="inlineStr"/>
     </row>
@@ -31829,7 +31829,7 @@
         <v>12</v>
       </c>
       <c r="C1158" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D1158" s="7" t="inlineStr">
         <is>
@@ -31838,11 +31838,11 @@
       </c>
       <c r="E1158" s="8" t="inlineStr">
         <is>
-          <t>단점</t>
+          <t>취업이 거의 연결됨</t>
         </is>
       </c>
       <c r="F1158" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G1158" s="6" t="inlineStr"/>
     </row>
@@ -31856,7 +31856,7 @@
         <v>12</v>
       </c>
       <c r="C1159" s="7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D1159" s="7" t="inlineStr">
         <is>
@@ -31865,11 +31865,11 @@
       </c>
       <c r="E1159" s="8" t="inlineStr">
         <is>
-          <t>회사가 정해진다.</t>
+          <t>단점</t>
         </is>
       </c>
       <c r="F1159" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G1159" s="6" t="inlineStr"/>
     </row>
@@ -31883,7 +31883,7 @@
         <v>12</v>
       </c>
       <c r="C1160" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1160" s="7" t="inlineStr">
         <is>
@@ -31892,11 +31892,11 @@
       </c>
       <c r="E1160" s="8" t="inlineStr">
         <is>
-          <t>진로 변경이 쉽지 않을 수 있다.</t>
+          <t>회사가 정해진다.</t>
         </is>
       </c>
       <c r="F1160" s="7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G1160" s="6" t="inlineStr"/>
     </row>
@@ -31910,7 +31910,7 @@
         <v>12</v>
       </c>
       <c r="C1161" s="7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D1161" s="7" t="inlineStr">
         <is>
@@ -31919,11 +31919,11 @@
       </c>
       <c r="E1161" s="8" t="inlineStr">
         <is>
-          <t>④ 기업 장학생</t>
+          <t>진로 변경이 쉽지 않을 수 있다.</t>
         </is>
       </c>
       <c r="F1161" s="7" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G1161" s="6" t="inlineStr"/>
     </row>
@@ -31937,7 +31937,7 @@
         <v>12</v>
       </c>
       <c r="C1162" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D1162" s="7" t="inlineStr">
         <is>
@@ -31946,11 +31946,11 @@
       </c>
       <c r="E1162" s="8" t="inlineStr">
         <is>
-          <t>예를 들면 삼성 GSAT LG 장학생 현대 장학생 이런 것들.</t>
+          <t>④ 기업 장학생</t>
         </is>
       </c>
       <c r="F1162" s="7" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="G1162" s="6" t="inlineStr"/>
     </row>
@@ -31964,7 +31964,7 @@
         <v>12</v>
       </c>
       <c r="C1163" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D1163" s="7" t="inlineStr">
         <is>
@@ -31973,11 +31973,11 @@
       </c>
       <c r="E1163" s="8" t="inlineStr">
         <is>
-          <t>대학원은 일반으로 다니고 기업에서 장학금을 준다.</t>
+          <t>예를 들면 삼성 GSAT LG 장학생 현대 장학생 이런 것들.</t>
         </is>
       </c>
       <c r="F1163" s="7" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G1163" s="6" t="inlineStr"/>
     </row>
@@ -31991,7 +31991,7 @@
         <v>12</v>
       </c>
       <c r="C1164" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D1164" s="7" t="inlineStr">
         <is>
@@ -32000,11 +32000,11 @@
       </c>
       <c r="E1164" s="8" t="inlineStr">
         <is>
-          <t>너에게 어떤 게 맞을까?</t>
+          <t>대학원은 일반으로 다니고 기업에서 장학금을 준다.</t>
         </is>
       </c>
       <c r="F1164" s="7" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G1164" s="6" t="inlineStr"/>
     </row>
@@ -32018,7 +32018,7 @@
         <v>12</v>
       </c>
       <c r="C1165" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D1165" s="7" t="inlineStr">
         <is>
@@ -32027,11 +32027,11 @@
       </c>
       <c r="E1165" s="8" t="inlineStr">
         <is>
-          <t>나는</t>
+          <t>너에게 어떤 게 맞을까?</t>
         </is>
       </c>
       <c r="F1165" s="7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G1165" s="6" t="inlineStr"/>
     </row>
@@ -32045,7 +32045,7 @@
         <v>12</v>
       </c>
       <c r="C1166" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1166" s="7" t="inlineStr">
         <is>
@@ -32054,11 +32054,11 @@
       </c>
       <c r="E1166" s="8" t="inlineStr">
         <is>
-          <t>가장 추천</t>
+          <t>나는</t>
         </is>
       </c>
       <c r="F1166" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1166" s="6" t="inlineStr"/>
     </row>
@@ -32072,7 +32072,7 @@
         <v>12</v>
       </c>
       <c r="C1167" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D1167" s="7" t="inlineStr">
         <is>
@@ -32081,11 +32081,11 @@
       </c>
       <c r="E1167" s="8" t="inlineStr">
         <is>
-          <t>학연과정 이야.</t>
+          <t>가장 추천</t>
         </is>
       </c>
       <c r="F1167" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1167" s="6" t="inlineStr"/>
     </row>
@@ -32099,7 +32099,7 @@
         <v>12</v>
       </c>
       <c r="C1168" s="7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D1168" s="7" t="inlineStr">
         <is>
@@ -32108,11 +32108,11 @@
       </c>
       <c r="E1168" s="8" t="inlineStr">
         <is>
-          <t>왜냐하면 너는 계속 "산업에 적용되는 AI"를 이야기했잖아.</t>
+          <t>학연과정 이야.</t>
         </is>
       </c>
       <c r="F1168" s="7" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G1168" s="6" t="inlineStr"/>
     </row>
@@ -32126,7 +32126,7 @@
         <v>12</v>
       </c>
       <c r="C1169" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D1169" s="7" t="inlineStr">
         <is>
@@ -32135,11 +32135,11 @@
       </c>
       <c r="E1169" s="8" t="inlineStr">
         <is>
-          <t>학연은 진짜 산업 문제를 푼다.</t>
+          <t>왜냐하면 너는 계속 "산업에 적용되는 AI"를 이야기했잖아.</t>
         </is>
       </c>
       <c r="F1169" s="7" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G1169" s="6" t="inlineStr"/>
     </row>
@@ -32153,7 +32153,7 @@
         <v>12</v>
       </c>
       <c r="C1170" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D1170" s="7" t="inlineStr">
         <is>
@@ -32162,11 +32162,11 @@
       </c>
       <c r="E1170" s="8" t="inlineStr">
         <is>
-          <t>예를 들면 현대차 ↓ Robot ↓ Vision ↓ LLM ↓ 공장 ↓ 자율주행 이런 연구를 한다.</t>
+          <t>학연은 진짜 산업 문제를 푼다.</t>
         </is>
       </c>
       <c r="F1170" s="7" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="G1170" s="6" t="inlineStr"/>
     </row>
@@ -32180,7 +32180,7 @@
         <v>12</v>
       </c>
       <c r="C1171" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D1171" s="7" t="inlineStr">
         <is>
@@ -32189,11 +32189,11 @@
       </c>
       <c r="E1171" s="8" t="inlineStr">
         <is>
-          <t>계약학과는?</t>
+          <t>예를 들면 현대차 ↓ Robot ↓ Vision ↓ LLM ↓ 공장 ↓ 자율주행 이런 연구를 한다.</t>
         </is>
       </c>
       <c r="F1171" s="7" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="G1171" s="6" t="inlineStr"/>
     </row>
@@ -32207,7 +32207,7 @@
         <v>12</v>
       </c>
       <c r="C1172" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D1172" s="7" t="inlineStr">
         <is>
@@ -32216,11 +32216,11 @@
       </c>
       <c r="E1172" s="8" t="inlineStr">
         <is>
-          <t>나는 회사가 정말 마음에 들면 추천.</t>
+          <t>계약학과는?</t>
         </is>
       </c>
       <c r="F1172" s="7" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G1172" s="6" t="inlineStr"/>
     </row>
@@ -32234,7 +32234,7 @@
         <v>12</v>
       </c>
       <c r="C1173" s="7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D1173" s="7" t="inlineStr">
         <is>
@@ -32243,11 +32243,11 @@
       </c>
       <c r="E1173" s="8" t="inlineStr">
         <is>
-          <t>예를 들면 삼성전자 DX 현대자동차 AI LG AI연구원 이런 곳.</t>
+          <t>나는 회사가 정말 마음에 들면 추천.</t>
         </is>
       </c>
       <c r="F1173" s="7" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G1173" s="6" t="inlineStr"/>
     </row>
@@ -32261,7 +32261,7 @@
         <v>12</v>
       </c>
       <c r="C1174" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D1174" s="7" t="inlineStr">
         <is>
@@ -32270,11 +32270,11 @@
       </c>
       <c r="E1174" s="8" t="inlineStr">
         <is>
-          <t>하지만 아직 "무슨 분야를 할지" 고민 중이라면 조금 이른 선택일 수도 있다.</t>
+          <t>예를 들면 삼성전자 DX 현대자동차 AI LG AI연구원 이런 곳.</t>
         </is>
       </c>
       <c r="F1174" s="7" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G1174" s="6" t="inlineStr"/>
     </row>
@@ -32288,7 +32288,7 @@
         <v>12</v>
       </c>
       <c r="C1175" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D1175" s="7" t="inlineStr">
         <is>
@@ -32297,11 +32297,11 @@
       </c>
       <c r="E1175" s="8" t="inlineStr">
         <is>
-          <t>너라면 내가 추천하는 순위</t>
+          <t>하지만 아직 "무슨 분야를 할지" 고민 중이라면 조금 이른 선택일 수도 있다.</t>
         </is>
       </c>
       <c r="F1175" s="7" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="G1175" s="6" t="inlineStr"/>
     </row>
@@ -32315,7 +32315,7 @@
         <v>12</v>
       </c>
       <c r="C1176" s="7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D1176" s="7" t="inlineStr">
         <is>
@@ -32324,11 +32324,11 @@
       </c>
       <c r="E1176" s="8" t="inlineStr">
         <is>
-          <t>🥇 1순위 일반 대학원 + AI 연구실 + 산학 프로젝트 많은 곳 🥈 2순위 학연과정 (연구소) 🥉 3순위 현대차 삼성 LG 계약학과</t>
+          <t>너라면 내가 추천하는 순위</t>
         </is>
       </c>
       <c r="F1176" s="7" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="G1176" s="6" t="inlineStr"/>
     </row>
@@ -32342,7 +32342,7 @@
         <v>12</v>
       </c>
       <c r="C1177" s="7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D1177" s="7" t="inlineStr">
         <is>
@@ -32351,11 +32351,11 @@
       </c>
       <c r="E1177" s="8" t="inlineStr">
         <is>
-          <t>그리고 하나 알려주고 싶은 게 있어.</t>
+          <t>🥇 1순위 일반 대학원 + AI 연구실 + 산학 프로젝트 많은 곳 🥈 2순위 학연과정 (연구소) 🥉 3순위 현대차 삼성 LG 계약학과</t>
         </is>
       </c>
       <c r="F1177" s="7" t="n">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="G1177" s="6" t="inlineStr"/>
     </row>
@@ -32369,7 +32369,7 @@
         <v>12</v>
       </c>
       <c r="C1178" s="7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D1178" s="7" t="inlineStr">
         <is>
@@ -32378,11 +32378,11 @@
       </c>
       <c r="E1178" s="8" t="inlineStr">
         <is>
-          <t>요즘 기업들도 "모델만 만드는 사람"보다 "도메인을 이해하는 AI 연구자"를 많이 찾는 추세야.</t>
+          <t>그리고 하나 알려주고 싶은 게 있어.</t>
         </is>
       </c>
       <c r="F1178" s="7" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="G1178" s="6" t="inlineStr"/>
     </row>
@@ -32396,7 +32396,7 @@
         <v>12</v>
       </c>
       <c r="C1179" s="7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D1179" s="7" t="inlineStr">
         <is>
@@ -32405,11 +32405,11 @@
       </c>
       <c r="E1179" s="8" t="inlineStr">
         <is>
-          <t>예를 들어 현대차에서는</t>
+          <t>요즘 기업들도 "모델만 만드는 사람"보다 "도메인을 이해하는 AI 연구자"를 많이 찾는 추세야.</t>
         </is>
       </c>
       <c r="F1179" s="7" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="G1179" s="6" t="inlineStr"/>
     </row>
@@ -32423,7 +32423,7 @@
         <v>12</v>
       </c>
       <c r="C1180" s="7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D1180" s="7" t="inlineStr">
         <is>
@@ -32432,11 +32432,11 @@
       </c>
       <c r="E1180" s="8" t="inlineStr">
         <is>
-          <t>Robot AI</t>
+          <t>예를 들어 현대차에서는</t>
         </is>
       </c>
       <c r="F1180" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G1180" s="6" t="inlineStr"/>
     </row>
@@ -32450,7 +32450,7 @@
         <v>12</v>
       </c>
       <c r="C1181" s="7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D1181" s="7" t="inlineStr">
         <is>
@@ -32459,11 +32459,11 @@
       </c>
       <c r="E1181" s="8" t="inlineStr">
         <is>
-          <t>Vision AI</t>
+          <t>Robot AI</t>
         </is>
       </c>
       <c r="F1181" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1181" s="6" t="inlineStr"/>
     </row>
@@ -32477,7 +32477,7 @@
         <v>12</v>
       </c>
       <c r="C1182" s="7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D1182" s="7" t="inlineStr">
         <is>
@@ -32486,11 +32486,11 @@
       </c>
       <c r="E1182" s="8" t="inlineStr">
         <is>
-          <t>Manufacturing AI</t>
+          <t>Vision AI</t>
         </is>
       </c>
       <c r="F1182" s="7" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G1182" s="6" t="inlineStr"/>
     </row>
@@ -32504,7 +32504,7 @@
         <v>12</v>
       </c>
       <c r="C1183" s="7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D1183" s="7" t="inlineStr">
         <is>
@@ -32513,11 +32513,11 @@
       </c>
       <c r="E1183" s="8" t="inlineStr">
         <is>
-          <t>Embodied AI</t>
+          <t>Manufacturing AI</t>
         </is>
       </c>
       <c r="F1183" s="7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G1183" s="6" t="inlineStr"/>
     </row>
@@ -32531,7 +32531,7 @@
         <v>12</v>
       </c>
       <c r="C1184" s="7" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D1184" s="7" t="inlineStr">
         <is>
@@ -32540,11 +32540,11 @@
       </c>
       <c r="E1184" s="8" t="inlineStr">
         <is>
-          <t>같은 분야를 많이 채용하고, 삼성전자에서는</t>
+          <t>Embodied AI</t>
         </is>
       </c>
       <c r="F1184" s="7" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G1184" s="6" t="inlineStr"/>
     </row>
@@ -32558,7 +32558,7 @@
         <v>12</v>
       </c>
       <c r="C1185" s="7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D1185" s="7" t="inlineStr">
         <is>
@@ -32567,11 +32567,11 @@
       </c>
       <c r="E1185" s="8" t="inlineStr">
         <is>
-          <t>온디바이스 AI</t>
+          <t>같은 분야를 많이 채용하고, 삼성전자에서는</t>
         </is>
       </c>
       <c r="F1185" s="7" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G1185" s="6" t="inlineStr"/>
     </row>
@@ -32585,7 +32585,7 @@
         <v>12</v>
       </c>
       <c r="C1186" s="7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D1186" s="7" t="inlineStr">
         <is>
@@ -32594,11 +32594,11 @@
       </c>
       <c r="E1186" s="8" t="inlineStr">
         <is>
-          <t>Vision AI</t>
+          <t>온디바이스 AI</t>
         </is>
       </c>
       <c r="F1186" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1186" s="6" t="inlineStr"/>
     </row>
@@ -32612,7 +32612,7 @@
         <v>12</v>
       </c>
       <c r="C1187" s="7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D1187" s="7" t="inlineStr">
         <is>
@@ -32621,11 +32621,11 @@
       </c>
       <c r="E1187" s="8" t="inlineStr">
         <is>
-          <t>AI Systems</t>
+          <t>Vision AI</t>
         </is>
       </c>
       <c r="F1187" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1187" s="6" t="inlineStr"/>
     </row>
@@ -32639,7 +32639,7 @@
         <v>12</v>
       </c>
       <c r="C1188" s="7" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1188" s="7" t="inlineStr">
         <is>
@@ -32648,11 +32648,11 @@
       </c>
       <c r="E1188" s="8" t="inlineStr">
         <is>
-          <t>같은 분야를 활발히 연구해.</t>
+          <t>AI Systems</t>
         </is>
       </c>
       <c r="F1188" s="7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G1188" s="6" t="inlineStr"/>
     </row>
@@ -32666,7 +32666,7 @@
         <v>12</v>
       </c>
       <c r="C1189" s="7" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1189" s="7" t="inlineStr">
         <is>
@@ -32675,11 +32675,11 @@
       </c>
       <c r="E1189" s="8" t="inlineStr">
         <is>
-          <t>LG AI연구원도 LLM뿐 아니라 산업 적용, 멀티모달, AI 에이전트 등으로 연구 범위를 넓히고 있어.</t>
+          <t>같은 분야를 활발히 연구해.</t>
         </is>
       </c>
       <c r="F1189" s="7" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G1189" s="6" t="inlineStr"/>
     </row>
@@ -32693,7 +32693,7 @@
         <v>12</v>
       </c>
       <c r="C1190" s="7" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D1190" s="7" t="inlineStr">
         <is>
@@ -32702,11 +32702,11 @@
       </c>
       <c r="E1190" s="8" t="inlineStr">
         <is>
-          <t>즉, 기업 연구소의 방향도 "현실 문제를 해결하는 AI"로 점점 확장되는 흐름이야.</t>
+          <t>LG AI연구원도 LLM뿐 아니라 산업 적용, 멀티모달, AI 에이전트 등으로 연구 범위를 넓히고 있어.</t>
         </is>
       </c>
       <c r="F1190" s="7" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="G1190" s="6" t="inlineStr"/>
     </row>
@@ -32720,7 +32720,7 @@
         <v>12</v>
       </c>
       <c r="C1191" s="7" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D1191" s="7" t="inlineStr">
         <is>
@@ -32729,11 +32729,11 @@
       </c>
       <c r="E1191" s="8" t="inlineStr">
         <is>
-          <t>내가 너에게 추천하고 싶은 전략</t>
+          <t>즉, 기업 연구소의 방향도 "현실 문제를 해결하는 AI"로 점점 확장되는 흐름이야.</t>
         </is>
       </c>
       <c r="F1191" s="7" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G1191" s="6" t="inlineStr"/>
     </row>
@@ -32747,7 +32747,7 @@
         <v>12</v>
       </c>
       <c r="C1192" s="7" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D1192" s="7" t="inlineStr">
         <is>
@@ -32756,11 +32756,11 @@
       </c>
       <c r="E1192" s="8" t="inlineStr">
         <is>
-          <t>너는 아직 진로를 확정하지 않았으니까 처음부터 계약학과 하나만 노리기보다, 아래처럼 준비하는 게 가장 유연해 보여.</t>
+          <t>내가 너에게 추천하고 싶은 전략</t>
         </is>
       </c>
       <c r="F1192" s="7" t="n">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="G1192" s="6" t="inlineStr"/>
     </row>
@@ -32774,7 +32774,7 @@
         <v>12</v>
       </c>
       <c r="C1193" s="7" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D1193" s="7" t="inlineStr">
         <is>
@@ -32783,11 +32783,11 @@
       </c>
       <c r="E1193" s="8" t="inlineStr">
         <is>
-          <t>일반 AI 대학원(로보틱스·Physical AI·Manufacturing AI 중심)을 우선 컨택한다.</t>
+          <t>너는 아직 진로를 확정하지 않았으니까 처음부터 계약학과 하나만 노리기보다, 아래처럼 준비하는 게 가장 유연해 보여.</t>
         </is>
       </c>
       <c r="F1193" s="7" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G1193" s="6" t="inlineStr"/>
     </row>
@@ -32801,7 +32801,7 @@
         <v>12</v>
       </c>
       <c r="C1194" s="7" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D1194" s="7" t="inlineStr">
         <is>
@@ -32810,11 +32810,11 @@
       </c>
       <c r="E1194" s="8" t="inlineStr">
         <is>
-          <t>동시에 학연과정(ETRI, KITECH, 현대차 협력 연구실 등)도 함께 알아본다.</t>
+          <t>일반 AI 대학원(로보틱스·Physical AI·Manufacturing AI 중심)을 우선 컨택한다.</t>
         </is>
       </c>
       <c r="F1194" s="7" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G1194" s="6" t="inlineStr"/>
     </row>
@@ -32828,7 +32828,7 @@
         <v>12</v>
       </c>
       <c r="C1195" s="7" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D1195" s="7" t="inlineStr">
         <is>
@@ -32837,11 +32837,11 @@
       </c>
       <c r="E1195" s="8" t="inlineStr">
         <is>
-          <t>올해와 내년에 나오는 삼성, 현대차, LG 계약학과 모집도 같이 지원한다.</t>
+          <t>동시에 학연과정(ETRI, KITECH, 현대차 협력 연구실 등)도 함께 알아본다.</t>
         </is>
       </c>
       <c r="F1195" s="7" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G1195" s="6" t="inlineStr"/>
     </row>
@@ -32855,7 +32855,7 @@
         <v>12</v>
       </c>
       <c r="C1196" s="7" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D1196" s="7" t="inlineStr">
         <is>
@@ -32864,11 +32864,11 @@
       </c>
       <c r="E1196" s="8" t="inlineStr">
         <is>
-          <t>이렇게 하면 연구 자유도도 확보하고, 기업 진출 기회도 놓치지 않을 수 있어.</t>
+          <t>올해와 내년에 나오는 삼성, 현대차, LG 계약학과 모집도 같이 지원한다.</t>
         </is>
       </c>
       <c r="F1196" s="7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G1196" s="6" t="inlineStr"/>
     </row>
@@ -32882,7 +32882,7 @@
         <v>12</v>
       </c>
       <c r="C1197" s="7" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D1197" s="7" t="inlineStr">
         <is>
@@ -32891,11 +32891,11 @@
       </c>
       <c r="E1197" s="8" t="inlineStr">
         <is>
-          <t>사실 내가 다음에 꼭 해주고 싶은 게 하나 있어.</t>
+          <t>이렇게 하면 연구 자유도도 확보하고, 기업 진출 기회도 놓치지 않을 수 있어.</t>
         </is>
       </c>
       <c r="F1197" s="7" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G1197" s="6" t="inlineStr"/>
     </row>
@@ -32909,7 +32909,7 @@
         <v>12</v>
       </c>
       <c r="C1198" s="7" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D1198" s="7" t="inlineStr">
         <is>
@@ -32918,11 +32918,11 @@
       </c>
       <c r="E1198" s="8" t="inlineStr">
         <is>
-          <t>"기업 기준"으로 AI 분야를 분석해보는 거야.</t>
+          <t>사실 내가 다음에 꼭 해주고 싶은 게 하나 있어.</t>
         </is>
       </c>
       <c r="F1198" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1198" s="6" t="inlineStr"/>
     </row>
@@ -32936,7 +32936,7 @@
         <v>12</v>
       </c>
       <c r="C1199" s="7" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D1199" s="7" t="inlineStr">
         <is>
@@ -32945,11 +32945,11 @@
       </c>
       <c r="E1199" s="8" t="inlineStr">
         <is>
-          <t>예를 들어</t>
+          <t>"기업 기준"으로 AI 분야를 분석해보는 거야.</t>
         </is>
       </c>
       <c r="F1199" s="7" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G1199" s="6" t="inlineStr"/>
     </row>
@@ -32963,7 +32963,7 @@
         <v>12</v>
       </c>
       <c r="C1200" s="7" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D1200" s="7" t="inlineStr">
         <is>
@@ -32972,11 +32972,11 @@
       </c>
       <c r="E1200" s="8" t="inlineStr">
         <is>
-          <t>현대차가 원하는 AI</t>
+          <t>예를 들어</t>
         </is>
       </c>
       <c r="F1200" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G1200" s="6" t="inlineStr"/>
     </row>
@@ -32990,7 +32990,7 @@
         <v>12</v>
       </c>
       <c r="C1201" s="7" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D1201" s="7" t="inlineStr">
         <is>
@@ -32999,11 +32999,11 @@
       </c>
       <c r="E1201" s="8" t="inlineStr">
         <is>
-          <t>삼성전자가 원하는 AI</t>
+          <t>현대차가 원하는 AI</t>
         </is>
       </c>
       <c r="F1201" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1201" s="6" t="inlineStr"/>
     </row>
@@ -33017,7 +33017,7 @@
         <v>12</v>
       </c>
       <c r="C1202" s="7" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D1202" s="7" t="inlineStr">
         <is>
@@ -33026,11 +33026,11 @@
       </c>
       <c r="E1202" s="8" t="inlineStr">
         <is>
-          <t>LG AI연구원이 원하는 AI</t>
+          <t>삼성전자가 원하는 AI</t>
         </is>
       </c>
       <c r="F1202" s="7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G1202" s="6" t="inlineStr"/>
     </row>
@@ -33044,7 +33044,7 @@
         <v>12</v>
       </c>
       <c r="C1203" s="7" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D1203" s="7" t="inlineStr">
         <is>
@@ -33053,11 +33053,11 @@
       </c>
       <c r="E1203" s="8" t="inlineStr">
         <is>
-          <t>네이버·카카오가 원하는 AI</t>
+          <t>LG AI연구원이 원하는 AI</t>
         </is>
       </c>
       <c r="F1203" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1203" s="6" t="inlineStr"/>
     </row>
@@ -33071,7 +33071,7 @@
         <v>12</v>
       </c>
       <c r="C1204" s="7" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D1204" s="7" t="inlineStr">
         <is>
@@ -33080,11 +33080,11 @@
       </c>
       <c r="E1204" s="8" t="inlineStr">
         <is>
-          <t>NVIDIA, Tesla 같은 해외 기업이 원하는 AI</t>
+          <t>네이버·카카오가 원하는 AI</t>
         </is>
       </c>
       <c r="F1204" s="7" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G1204" s="6" t="inlineStr"/>
     </row>
@@ -33098,28 +33098,82 @@
         <v>12</v>
       </c>
       <c r="C1205" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="D1205" s="7" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E1205" s="8" t="inlineStr">
+        <is>
+          <t>NVIDIA, Tesla 같은 해외 기업이 원하는 AI</t>
+        </is>
+      </c>
+      <c r="F1205" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1205" s="6" t="inlineStr"/>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="7" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B1206" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1206" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="D1205" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E1205" s="8" t="inlineStr">
+      <c r="D1206" s="7" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E1206" s="8" t="inlineStr">
         <is>
           <t>를 비교해서, 어떤 대학원 분야를 선택해야 어느 회사까지 갈 수 있는지를 연결해서 보여주면, 지금보다 훨씬 방향을 잡기 쉬울 거라고 생각해.</t>
         </is>
       </c>
-      <c r="F1205" s="7" t="n">
+      <c r="F1206" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="G1205" s="6" t="inlineStr"/>
+      <c r="G1206" s="6" t="inlineStr"/>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="7" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B1207" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1207" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="D1207" s="7" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E1207" s="8" t="inlineStr">
+        <is>
+          <t>Powered by ChatGPT Exporter</t>
+        </is>
+      </c>
+      <c r="F1207" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1207" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <autoFilter ref="A1:G1205"/>
+  <autoFilter ref="A1:G1207"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G1205" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="코드 아님" error="ESConv 8개 코드 중에서 고르세요." promptTitle="esconv" prompt="QST RST RFL SLF AFF SUG INF OTH" type="list">
+    <dataValidation sqref="G2:G1207" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="코드 아님" error="ESConv 8개 코드 중에서 고르세요." promptTitle="esconv" prompt="QST RST RFL SLF AFF SUG INF OTH" type="list">
       <formula1>"QST,RST,RFL,SLF,AFF,SUG,INF,OTH"</formula1>
     </dataValidation>
   </dataValidations>
